--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC359B79-7A1E-4B74-8961-9CE1E381C6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D653315-9C3D-4BB0-8D22-C4FE9CA68334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3863,29 +3863,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4301,7 +4301,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>23.32</v>
+        <v>23.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11796.540745440001</v>
+        <v>11973.590027640001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4359,13 +4359,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10265688775118464</v>
+        <v>9.6969308965579426E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>11.7960473130998</v>
+        <v>13.438941031541804</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4490,7 +4490,7 @@
         <v>429</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>17.445104340862148</v>
+        <v>18.869653870203344</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4509,7 +4509,7 @@
         <v>442</v>
       </c>
       <c r="F30" s="342">
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>22.295532459418446</v>
+        <v>24.301055185803946</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4547,7 +4547,7 @@
         <v>443</v>
       </c>
       <c r="F32" s="342">
-        <v>0.12</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4565,22 +4565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4592,13 +4592,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4618,13 +4618,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4653,13 +4653,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4675,13 +4675,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4745,13 +4745,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4767,7 +4767,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="351"/>
@@ -4789,22 +4789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.6786488926852473E-2</v>
+        <v>5.5946807003557232E-2</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.4782425010561892E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>453</v>
@@ -4873,22 +4873,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4932,22 +4932,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4984,13 +4984,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>369</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5003,13 +5003,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5140,13 +5140,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5185,13 +5185,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>371</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5334,13 +5334,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>374</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5353,22 +5353,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>372</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>1.6842565597667636</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>10.111790753333036</v>
+        <v>11.609618781212262</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>11.7960473130998</v>
+        <v>13.438941031541804</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.57486748227970297</v>
+        <v>0.51565717866448546</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>2.1647759063533951</v>
+        <v>2.279132885208865</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>15.280328434508752</v>
+        <v>16.59052098499448</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>17.445104340862148</v>
+        <v>18.869653870203344</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37127404345964066</v>
+        <v>0.31993291944146818</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C165" s="92">
         <f>F32</f>
-        <v>0.12</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>2.5459411443148712</v>
+        <v>2.6975834619563113</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>19.749591315103576</v>
+        <v>21.603471723847637</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>22.295532459418446</v>
+        <v>24.301055185803946</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.1965605777108882</v>
+        <v>0.12428977531548846</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5701,13 +5701,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>380</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>385</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5758,22 +5758,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>386</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>387</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5797,17 +5797,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5824,6 +5813,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.4782425010561892E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.4782425010561892E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14570,50 +14570,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6786488926852473E-2</v>
+        <v>5.5946807003557232E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3608747731656844E-2</v>
+        <v>5.2816053954467153E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9324510592065079E-2</v>
+        <v>4.8595166328980047E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.4781927161713423E-2</v>
+        <v>6.3824019493500514E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>5.9999011715634237E-2</v>
+        <v>5.9111827342990725E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4603074797751817E-2</v>
+        <v>5.3795678254481297E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7895873816182875E-2</v>
+        <v>3.733552080242436E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4267877297461393E-2</v>
+        <v>2.3909036695259806E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0131863494965783E-2</v>
+        <v>1.983418068029582E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3849382295293063E-2</v>
+        <v>2.3496729832118049E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.4994867000648187E-2</v>
+        <v>2.4625276656320898E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14627,43 +14627,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2065883579355283E-2</v>
+        <v>7.100027059867195E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8085284858653908E-2</v>
+        <v>6.7078531597119101E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2943172164960374E-2</v>
+        <v>8.1716720527540171E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8813344188158621E-2</v>
+        <v>7.7647958870631972E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8244318090554978E-2</v>
+        <v>6.723521326031863E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1157121059686624E-2</v>
+        <v>5.0400678627456355E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7432194872101872E-2</v>
+        <v>3.6878698116494114E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7269607416424122E-2</v>
+        <v>2.6866381282256466E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.043567811511071E-2</v>
+        <v>2.9985636402381988E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0954298033612233E-2</v>
+        <v>3.0496587669786111E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-23.32</v>
+        <v>-23.67</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>23.32</v>
+        <v>23.67</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19162,7 +19162,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6842565597667636</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19183,7 +19183,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.111790753333036</v>
+        <v>11.609618781212262</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19193,7 +19193,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>11.7960473130998</v>
+        <v>13.438941031541804</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19204,7 +19204,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.57486748227970297</v>
+        <v>0.51565717866448546</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>23.32</v>
+        <v>23.67</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10265688775118464</v>
+        <v>9.6969308965579426E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19260,7 +19260,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.1647759063533951</v>
+        <v>2.279132885208865</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -19272,7 +19272,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>15.280328434508752</v>
+        <v>16.59052098499448</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19282,7 +19282,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>17.445104340862148</v>
+        <v>18.869653870203344</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19293,7 +19293,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.37127404345964066</v>
+        <v>0.31993291944146818</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
-        <v>0.12</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.5459411443148712</v>
+        <v>2.6975834619563113</v>
       </c>
       <c r="D103" s="117"/>
     </row>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>19.749591315103576</v>
+        <v>21.603471723847637</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -19400,7 +19400,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>22.295532459418446</v>
+        <v>24.301055185803946</v>
       </c>
       <c r="D105" t="s">
         <v>400</v>
@@ -19410,7 +19410,7 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.1965605777108882</v>
+        <v>0.12428977531548846</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDCFDDC-5DC1-4CEE-BBAF-A2461D3880AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105BD3B3-C840-42B6-B0F7-10D5123F897E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4308,7 +4308,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>23.67</v>
+        <v>23.43</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11973.590027640001</v>
+        <v>11852.18480556</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4366,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>9.6969308965579426E-2</v>
+        <v>0.10085683037892057</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4497,7 +4497,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="305">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4572,22 +4572,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4599,13 +4599,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4625,13 +4625,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4660,13 +4660,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4752,13 +4752,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4796,22 +4796,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.5946807003557232E-2</v>
+        <v>5.6519885692454114E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.4782425010561892E-2</v>
+        <v>4.5241143832693134E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4880,22 +4880,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4939,22 +4939,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4991,13 +4991,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5010,13 +5010,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5147,13 +5147,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5192,13 +5192,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5341,13 +5341,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5360,22 +5360,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C137" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C141" s="299">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="C142" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5708,13 +5708,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5751,13 +5751,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5765,22 +5765,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5804,6 +5804,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5820,17 +5831,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13378,12 +13378,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.4782425010561892E-2</v>
+        <v>4.5241143832693134E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.4782425010561892E-2</v>
+        <v>4.5241143832693134E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14577,50 +14577,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.5946807003557232E-2</v>
+        <v>5.6519885692454114E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.2816053954467153E-2</v>
+        <v>5.3357063470005871E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.8595166328980047E-2</v>
+        <v>4.9092940119801864E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.3824019493500514E-2</v>
+        <v>6.4477786658606789E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>5.9111827342990725E-2</v>
+        <v>5.9717326214621877E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.3795678254481297E-2</v>
+        <v>5.4346722333912613E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.733552080242436E-2</v>
+        <v>3.7717958915637416E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.3909036695259806E-2</v>
+        <v>2.4153943601229178E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.983418068029582E-2</v>
+        <v>2.0037347703909608E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3496729832118049E-2</v>
+        <v>2.3737413364329246E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.4625276656320898E-2</v>
+        <v>2.4877520207217913E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14634,43 +14634,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.100027059867195E-2</v>
+        <v>7.1727546097762065E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7078531597119101E-2</v>
+        <v>6.7765635633965399E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1716720527540171E-2</v>
+        <v>8.2553767600805641E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7647958870631972E-2</v>
+        <v>7.844332848774474E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.723521326031863E-2</v>
+        <v>6.7923922230974917E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0400678627456355E-2</v>
+        <v>5.0916946782411106E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6878698116494114E-2</v>
+        <v>3.72564568680075E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6866381282256466E-2</v>
+        <v>2.7141581090525422E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9985636402381988E-2</v>
+        <v>3.0292787607528033E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0496587669786111E-2</v>
+        <v>3.0808972690731427E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18390,7 +18390,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.67</v>
+        <v>-23.43</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.67</v>
+        <v>23.43</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19169,7 +19169,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19178,7 +19178,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19228,7 +19228,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.67</v>
+        <v>23.43</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.6969308965579426E-2</v>
+        <v>0.10085683037892057</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC99728-603A-406D-A61C-6B84FB7DB30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D4ABEC-9683-417D-8F68-E5C8EB23038B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4322,7 +4322,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>23.43</v>
+        <v>23.21</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11852.18480556</v>
+        <v>11740.89668532</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10085683037892057</v>
+        <v>0.10446861407025998</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4511,7 +4511,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4586,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,13 +4613,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4639,13 +4639,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4810,22 +4810,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.6519885692454114E-2</v>
+        <v>5.7055619206126659E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5241143832693134E-2</v>
+        <v>4.5669969840585953E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4960,22 +4960,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5019,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5071,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5218,13 +5218,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5263,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5412,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5431,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5779,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5822,13 +5822,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5836,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,6 +5875,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5891,17 +5902,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5241143832693134E-2</v>
+        <v>4.5669969840585953E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5241143832693134E-2</v>
+        <v>4.5669969840585953E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14648,50 +14648,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6519885692454114E-2</v>
+        <v>5.7055619206126659E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3357063470005871E-2</v>
+        <v>5.386281762611967E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9092940119801864E-2</v>
+        <v>4.9558276045108041E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.4477786658606789E-2</v>
+        <v>6.5088950513190746E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>5.9717326214621877E-2</v>
+        <v>6.0283367221395538E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4346722333912613E-2</v>
+        <v>5.4861857142764862E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7717958915637416E-2</v>
+        <v>3.8075475113889902E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4153943601229178E-2</v>
+        <v>2.4382890933942251E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0037347703909608E-2</v>
+        <v>2.0227275170297376E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3737413364329246E-2</v>
+        <v>2.3962412543138054E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.4877520207217913E-2</v>
+        <v>2.5113326085959314E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14705,43 +14705,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1727546097762065E-2</v>
+        <v>7.2407428051295353E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7765635633965399E-2</v>
+        <v>6.8407963933813418E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2553767600805641E-2</v>
+        <v>8.3336267767637917E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.844332848774474E-2</v>
+        <v>7.9186867146396347E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7923922230974917E-2</v>
+        <v>6.8567750877714023E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0916946782411106E-2</v>
+        <v>5.1399571870396045E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.72564568680075E-2</v>
+        <v>3.7609598639268237E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7141581090525422E-2</v>
+        <v>2.7398847261999596E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0292787607528033E-2</v>
+        <v>3.0579923035087539E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0808972690731427E-2</v>
+        <v>3.110100086789476E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18461,7 +18461,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.43</v>
+        <v>-23.21</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.43</v>
+        <v>23.21</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.43</v>
+        <v>23.21</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10085683037892057</v>
+        <v>0.10446861407025998</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D4ABEC-9683-417D-8F68-E5C8EB23038B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A147F4-CAD1-408D-BD3B-47E4307F92D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3880,6 +3854,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4380,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4511,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,19 +4629,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>923979255.39561176</v>
       </c>
@@ -4639,19 +4655,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
@@ -4664,7 +4680,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
@@ -4674,19 +4690,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4696,19 +4712,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>32042840.928504106</v>
       </c>
@@ -4723,7 +4739,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-59672121</v>
       </c>
@@ -4738,7 +4754,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-27629280.071495894</v>
       </c>
@@ -4756,7 +4772,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-2378351.0769942678</v>
       </c>
@@ -4766,19 +4782,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-224087493.83102897</v>
       </c>
@@ -4788,19 +4804,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4810,28 +4826,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>632397776.92850411</v>
       </c>
@@ -4844,7 +4860,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>669884130.41609263</v>
       </c>
@@ -4883,10 +4899,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4908,11 +4924,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.13375671427886937</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.12092451547494525</v>
       </c>
@@ -4922,11 +4938,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.66633267926556194</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.70909055913759678</v>
       </c>
@@ -4936,11 +4952,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.7557268340491488</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.7557268340491488</v>
       </c>
@@ -4960,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,19 +5106,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>2209595736.0500002</v>
       </c>
@@ -5128,7 +5144,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.3857437197038544</v>
       </c>
@@ -5137,7 +5153,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>2.3913910654887354</v>
       </c>
@@ -5151,7 +5167,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>4583178463.29</v>
       </c>
@@ -5164,7 +5180,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>3530916331.352602</v>
       </c>
@@ -5195,7 +5211,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>590585139.73500001</v>
       </c>
@@ -5218,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.829322250329541</v>
+        <v>1.8293222503295408</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5793,13 +5809,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5822,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6017,397 +6033,397 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>7131364079</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>6805627279</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>6883365208</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>5985026032</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>5289304050</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>4837252294</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>4197045559</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>3602738165</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>3513011838</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>3311372570</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>5145338820</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>5036852503</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>4741732369</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>4125460517</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>3648371932</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>3274676386</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>2935100815</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>2568541074</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>2462409261</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>2258759022</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>1020355341</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>905855866</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>1042555140</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>870066331</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>759567420</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>914353673</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>786040676</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>698786559</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>653103605</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>647456178</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>712355118</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>616499772</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>700587939</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>604192141</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>516475958</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>666000728</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>569962537</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>488865088</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>450745526</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>432888482</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>75683892</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>64604520</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>53560452</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>45085492</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>36242796</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>30636524</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>25189552</v>
       </c>
-      <c r="J8" s="334">
-        <v>0</v>
-      </c>
-      <c r="K8" s="334">
-        <v>0</v>
-      </c>
-      <c r="L8" s="334">
-        <v>0</v>
-      </c>
-      <c r="M8" s="334"/>
+      <c r="J8" s="321">
+        <v>0</v>
+      </c>
+      <c r="K8" s="321">
+        <v>0</v>
+      </c>
+      <c r="L8" s="321">
+        <v>0</v>
+      </c>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>59672121</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>55482330</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>54113032</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>57135193</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>20257228</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>14761326</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>33195116</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>139564139</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>133949036</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>75916153</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>81878485</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>49513640</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>29229712</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>37107822</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>229311604</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>191295542</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>242188379</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>197232207</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>192105224</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>162495080</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>131000165</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>95459293</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>110832660</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>109092609</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>850128132</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>803170837</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>978442510</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>929724826</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>805046879</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>603477063</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>441570412</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>321687035</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>359035717</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>365153638</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>647365</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>431576</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>2442951</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>1064169</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>-67938</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>-48477</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>8761899</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>2464891</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>5326102</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>1211794</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6419,157 +6435,157 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334"/>
-      <c r="D19" s="334"/>
-      <c r="E19" s="334"/>
-      <c r="F19" s="334"/>
-      <c r="G19" s="334"/>
-      <c r="H19" s="334"/>
-      <c r="I19" s="334"/>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="C19" s="321"/>
+      <c r="D19" s="321"/>
+      <c r="E19" s="321"/>
+      <c r="F19" s="321"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>1038904494</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>419277594</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>1532242670</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>1344822756</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>596854422</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>646284830</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>746820878</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>292923529</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>472353645</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>266727845</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-581740675</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>1111872716</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>313454337</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-596185154</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-178162782</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-152623096</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-291851861</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-363586849</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>341081432</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-135754035</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-435769097</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-203084462</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-532792445</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-222928124</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>517207059</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-634956157</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-324343319</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>96730747</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-854943133</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>-254787292</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6603,186 +6619,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>488915470.69999999</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>422673488</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>456344428</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>319728461</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>217535243</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>224562135</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>179925262</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>189740348</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>149960778</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>123329934</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>1545872989.1700001</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>1623301115</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>984697312</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>1462249097</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>1687299780</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>1389523101</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>1209137008</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>1068705861</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>1085846527</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>1183037453</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>4328912448.4399996</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>3866253573</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>3275808581</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>3276083890</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>2771099894</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>1753709637</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>1768910685</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>1542190319</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>1188658961</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>1649560528</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>5728144421.2400007</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>5532519580</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>5271499220</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>4796138023</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>4207884703</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>3654994884</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>3359220783</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>3131686328</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>3031482304</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>2931250841</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>2154785.64</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>3206458</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>2776011</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>1702867</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>638758</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>703065</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>33066516</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>68702668</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>82250087</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>77231819</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6809,47 +6825,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>7131364079</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>6805627279</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>6883365208</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>5985026032</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>5289304050</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>4837252294</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>4197045559</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>3602738165</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>3513011838</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>3311372570</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6858,47 +6874,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-5145338820</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-5036852503</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-4741732369</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-4125460517</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-3648371932</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-3274676386</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-2935100815</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-2568541074</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-2462409261</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-2258759022</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6907,47 +6923,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>1986025259</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>1768774776</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>2141632839</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>1859565515</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>1640932118</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>1562575908</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>1261944744</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>1034197091</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>1050602577</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>1052613548</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6956,47 +6972,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-1020355341</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-905855866</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-1042555140</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-870066331</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-759567420</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-914353673</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-786040676</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-698786559</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-653103605</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-647456178</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7005,47 +7021,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-712355118</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-616499772</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-700587939</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-604192141</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-516475958</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-666000728</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-569962537</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-488865088</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-450745526</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-432888482</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7054,47 +7070,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-308000223</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-289356094</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-341967201</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-265874190</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-243091462</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-248352945</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-216078139</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-209921471</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-202358079</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-214567696</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7103,47 +7119,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-75683892</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-64604520</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-53560452</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-45085492</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-36242796</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-30636524</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-25189552</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7152,47 +7168,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>889986026</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>798314390</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>1045517247</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>944413692</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>845121902</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>617585711</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>450714516</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>335410532</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>397498972</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>405157370</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7299,47 +7315,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-229311604</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-191295542</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-242188379</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-197232207</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-192105224</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-162495080</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-131000165</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-95459293</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-110832660</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-109092609</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7348,47 +7364,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>850128132</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>803170837</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>978442510</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>929724826</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>805046879</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>603477063</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>441570412</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>321687035</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>359035717</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>365153638</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7397,47 +7413,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-647365</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>-431576</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>-2442951</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-1064169</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>-8761899</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>-2464891</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>-5326102</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-1211794</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7451,47 +7467,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-59672121</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-55482330</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-54113032</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-57135193</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-20257228</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-14761326</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-33195116</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7500,47 +7516,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>139564139</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>133949036</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>75916153</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>81878485</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>49513640</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>29229712</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>37107822</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7756,47 +7772,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>0</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7805,47 +7821,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7854,47 +7870,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7903,47 +7919,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>21394722</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>1328065848</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>1312904562</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>525709478</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>935898699</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>-141294423</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>130625698</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>26067427</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>-41508056</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>-123813482</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8325,115 +8341,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>488915470.69999999</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>422673488</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>456344428</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>319728461</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>217535243</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>224562135</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>1545872989.1700001</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>1623301115</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>984697312</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>1462249097</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>1687299780</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>1389523101</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>4328912448.4399996</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>3866253573</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>3275808581</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>3276083890</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>2771099894</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>1753709637</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>1768910685</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>1542190319</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>1188658961</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>1649560528</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8442,47 +8458,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>5728144421.2400007</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>5532519580</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>5271499220</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>4796138023</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>4207884703</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>3654994884</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>3359220783</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>3131686328</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>3031482304</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>2931250841</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9565,11 +9581,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-564798704.21000004</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-526131065.96869904</v>
       </c>
@@ -9597,8 +9613,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>1052262131.9373981</v>
       </c>
@@ -9902,54 +9918,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)</f>
         <v>6701345649.5</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>7131364079</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>6805627279</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>6883365208</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>5985026032</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>5289304050</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>4837252294</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>4197045559</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>3602738165</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>3513011838</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>3311372570</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9959,52 +9975,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-5416333378.1043882</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5857693938</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-5653352275</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-5442320308</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-4729652658</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-4164847890</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-3940677114</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-3505063352</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-3057406162</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-2913154787</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-2691647504</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10014,52 +10030,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>1285012271.3956118</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>1273670141</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>1152275004</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>1441044900</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>1255373374</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>1124456160</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>896575180</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>691982207</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>545332003</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>599857051</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>619725066</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10069,52 +10085,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-361033016</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-383684115</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-353960614</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-395527653</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-310959682</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-279334258</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-278989469</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-241267691</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-209921471</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-202358079</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-214567696</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10124,54 +10140,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>923979255.39561176</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>889986026</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>798314390</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>1045517247</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>944413692</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>845121902</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>617585711</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>450714516</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>335410532</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>397498972</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>405157370</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10181,52 +10197,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10236,52 +10252,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>0</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>0</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>0</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>0</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>0</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>0</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>0</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>0</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10291,54 +10307,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10348,52 +10364,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-27629280.071495894</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>-27629280.071495891</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-24728673.051817413</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-36683273.668721363</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-38336529.610388793</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>-8889281.3220126256</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-8050411.4433459612</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-24675448.655158319</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10403,52 +10419,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>896349975.32411587</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>862356745.92850411</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>773585716.94818258</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>1008833973.3312787</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>906077162.38961124</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>836232620.67798734</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>609535299.5566541</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>426039067.34484166</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>335410532</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>397498972</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>405157370</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10458,52 +10474,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-224087493.83102897</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-229311604</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-191295542</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-242188379</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-197232207</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-192105224</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-162495080</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-131000165</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-95459293</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-110832660</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-109092609</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10513,54 +10529,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-2378351.0769942678</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-647365</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>-431576</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>-2442951</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-1064169</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>-8761899</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>-2464891</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>-5326102</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-1211794</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10570,54 +10586,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>669884130.41609263</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>632397776.92850411</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>581858598.94818258</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>764202643.33127868</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>707780786.38961124</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>644127396.67798734</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>447040219.5566541</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>286277003.34484166</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>237486348</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>281340210</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>294852967</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10627,7 +10643,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10636,24 +10652,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10661,71 +10677,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>669884130.41609263</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>632397776.92850411</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>581858598.94818258</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>764202643.33127868</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>707780786.38961124</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>644127396.67798734</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>447040219.5566541</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>286277003.34484166</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>237486348</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>281340210</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>294852967</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10798,54 +10814,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-4757578204.6885996</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-5145338820</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-5036852503</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-4741732369</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-4125460517</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-3648371932</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-3274676386</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-2935100815</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-2568541074</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-2462409261</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-2258759022</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10855,54 +10871,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-658755173.41578829</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-712355118</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-616499772</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-700587939</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-604192141</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-516475958</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-666000728</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-569962537</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-488865088</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-450745526</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-432888482</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10912,54 +10928,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-5416333378.1043882</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-5857693938</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-5653352275</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-5442320308</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-4729652658</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-4164847890</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-3940677114</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-3505063352</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-3057406162</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-2913154787</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-2691647504</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11165,54 +11181,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:J33)</f>
         <v>-301299427</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-308000223</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-289356094</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-341967201</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-265874190</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-243091462</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-248352945</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-216078139</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-209921471</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-202358079</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-214567696</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11222,7 +11238,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>-59733589</v>
       </c>
@@ -11231,47 +11247,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-75683892</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-64604520</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-53560452</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-45085492</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-36242796</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-30636524</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-25189552</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11281,54 +11297,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-361033016</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-383684115</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-353960614</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-395527653</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-310959682</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-279334258</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-278989469</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-241267691</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-209921471</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-202358079</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-214567696</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11622,52 +11638,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-59672121</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-59672121</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-55482330</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-54113032</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-57135193</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-20257228</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-14761326</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-33195116</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11677,52 +11693,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>32042840.928504106</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>32042840.928504109</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>30753656.948182587</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>17429758.331278637</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>18798663.389611207</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>11367946.677987374</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>6710914.5566540388</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>8519667.3448416796</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11732,54 +11748,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>139564139</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>139564139</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>133949036</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>75916153</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>81878485</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>49513640</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>29229712</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>37107822</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11789,52 +11805,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-27629280.071495894</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-27629280.071495891</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-24728673.051817413</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-36683273.668721363</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-38336529.610388793</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>-8889281.3220126256</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-8050411.4433459612</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-24675448.655158319</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11981,52 +11997,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12036,52 +12052,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12091,52 +12107,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12146,52 +12162,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12201,53 +12217,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>109561692</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>117685283</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>153310521</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>157800049</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>122773789</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>133918046</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>117943355</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>81735796</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>72369405</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>69088877</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12257,52 +12273,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>109561692</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>117685283</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>153310521</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>157800049</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>122773789</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>133918046</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>117943355</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>81735796</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>72369405</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>69088877</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13677,54 +13693,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>10057056869.68</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>10057056869.68</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>9398773153</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>8547307801</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>8072221913</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>6978984597</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>5408704521</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>5128131468</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>4673876647</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>4220141265</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>4580811369</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13734,54 +13750,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>488915470.69999999</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>422673488</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>456344428</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>319728461</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>217535243</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>224562135</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13791,54 +13807,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>1545872989.1700001</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>1623301115</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>984697312</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1462249097</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1687299780</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>1389523101</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13848,54 +13864,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>4328912448.4399996</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>4328912448.4399996</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>3866253573</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>3275808581</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>3276083890</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>2771099894</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>1753709637</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>1768910685</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>1542190319</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>1188658961</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>1649560528</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13905,54 +13921,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>5728144421.2400007</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>5728144421.2400007</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>5532519580</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>5271499220</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>4796138023</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>4207884703</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>3654994884</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>3359220783</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>3131686328</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>3031482304</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>2931250841</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15450,7 +15466,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15489,7 +15505,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>669884130.41609263</v>
       </c>
@@ -15521,7 +15537,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>11164735506.934877</v>
       </c>
@@ -15529,17 +15545,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>2209595736.0500002</v>
       </c>
@@ -15547,15 +15563,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>3530916331.352602</v>
       </c>
@@ -15563,15 +15579,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>590585139.73500001</v>
       </c>
@@ -15579,15 +15595,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>13076641241.972479</v>
       </c>
@@ -15654,7 +15670,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15664,7 +15680,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15678,10 +15694,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15699,7 +15715,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15721,7 +15737,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15743,7 +15759,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15763,9 +15779,19 @@
         <f t="shared" si="1"/>
         <v>662731563.44102097</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15785,9 +15811,19 @@
         <f t="shared" si="1"/>
         <v>660364386.06290972</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15807,9 +15843,19 @@
         <f t="shared" si="1"/>
         <v>658005663.88604224</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15831,7 +15877,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15853,7 +15899,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15875,7 +15921,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15897,7 +15943,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15919,7 +15965,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15941,7 +15987,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15963,11 +16009,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15983,13 +16029,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16005,13 +16061,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16027,9 +16093,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16051,7 +16127,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16073,7 +16149,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16095,7 +16171,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16117,7 +16193,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16139,7 +16215,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16161,7 +16237,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16183,7 +16259,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16205,7 +16281,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16227,7 +16303,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16249,7 +16325,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16271,11 +16347,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16291,13 +16367,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16313,13 +16399,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16335,13 +16431,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16357,9 +16463,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16381,7 +16497,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16392,11 +16508,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16406,7 +16522,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>12125628782.891102</v>
@@ -16433,7 +16549,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16455,7 +16571,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16476,14 +16592,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>11164735506.934868</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>12240871940.424587</v>
       </c>
       <c r="D58" s="123">
@@ -16495,16 +16611,26 @@
       <c r="F58" s="123">
         <v>16738447922.417589</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>11164735506.934868</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>12718341118.614334</v>
       </c>
       <c r="D59" s="123">
@@ -16516,16 +16642,26 @@
       <c r="F59" s="123">
         <v>20157578776.126354</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>11164735506.934868</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>13205676061.897917</v>
       </c>
       <c r="D60" s="123">
@@ -16537,16 +16673,26 @@
       <c r="F60" s="123">
         <v>24357646016.653687</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>11164735506.934868</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>13677542754.793108</v>
       </c>
       <c r="D61" s="123">
@@ -16558,26 +16704,56 @@
       <c r="F61" s="123">
         <v>29302439936.778774</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16949,6 +17125,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17051,7 +17297,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>8936773292.0000019</v>
       </c>
@@ -17059,8 +17305,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18517,7 +18763,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>889986026</v>
       </c>
@@ -18525,11 +18771,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洽洽食品(002557.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18542,7 +18788,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>632397776.92850411</v>
       </c>
@@ -18550,8 +18796,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18564,7 +18810,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>669884130.41609263</v>
       </c>
@@ -18572,8 +18818,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18583,8 +18829,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18597,8 +18843,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18616,8 +18862,8 @@
         <v>6.0153753070249838E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18634,8 +18880,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9591718766888921E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18652,8 +18898,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.6842771130545571E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18679,21 +18925,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18707,8 +18953,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18722,8 +18968,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18743,8 +18989,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18754,8 +19000,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18769,8 +19015,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18780,8 +19026,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18801,8 +19047,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18812,8 +19058,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18827,8 +19073,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18838,8 +19084,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18859,8 +19105,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18870,8 +19116,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18885,8 +19131,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18897,8 +19143,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18960,8 +19206,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18971,8 +19217,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18986,8 +19232,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18997,8 +19243,8 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19018,8 +19264,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19029,8 +19275,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19044,8 +19290,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19055,8 +19301,8 @@
         <v>0.15</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19240,7 +19486,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19249,7 +19495,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.829322250329541</v>
+        <v>1.8293222503295408</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A147F4-CAD1-408D-BD3B-47E4307F92D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67698CFF-73BA-4A55-AE46-461567974A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>23.21</v>
+        <v>22.99</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11740.89668532</v>
+        <v>11629.60856508</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10446861407025998</v>
+        <v>0.10812760515631625</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4527,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.7055619206126659E-2</v>
+        <v>5.7601605992788157E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5669969840585953E-2</v>
+        <v>4.6107003044802093E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5669969840585953E-2</v>
+        <v>4.6107003044802093E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5669969840585953E-2</v>
+        <v>4.6107003044802093E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14664,50 +14664,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7055619206126659E-2</v>
+        <v>5.7601605992788157E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.386281762611967E-2</v>
+        <v>5.4378251287613644E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9558276045108041E-2</v>
+        <v>5.003251792113779E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.5088950513190746E-2</v>
+        <v>6.5711811283651902E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.0283367221395538E-2</v>
+        <v>6.0860241548873012E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4861857142764862E-2</v>
+        <v>5.5386850991020989E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8075475113889902E-2</v>
+        <v>3.843983372741995E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4382890933942251E-2</v>
+        <v>2.4616220033788591E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0227275170297376E-2</v>
+        <v>2.0420837612118405E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3962412543138054E-2</v>
+        <v>2.4191717926325979E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.5113326085959314E-2</v>
+        <v>2.5353644995872802E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14721,43 +14721,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2407428051295353E-2</v>
+        <v>7.3100322099633103E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8407963933813418E-2</v>
+        <v>6.9062585598251819E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3336267767637917E-2</v>
+        <v>8.4133744014218192E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9186867146396347E-2</v>
+        <v>7.9944636209998227E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8567750877714023E-2</v>
+        <v>6.9223901603816543E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1399571870396045E-2</v>
+        <v>5.1891433802170164E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7609598639268237E-2</v>
+        <v>3.7969499104715775E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7398847261999596E-2</v>
+        <v>2.7661037187951744E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0579923035087539E-2</v>
+        <v>3.0872553877528568E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.110100086789476E-2</v>
+        <v>3.1398618101080356E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18707,7 +18707,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.21</v>
+        <v>-22.99</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.21</v>
+        <v>22.99</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19495,7 +19495,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.21</v>
+        <v>22.99</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10446861407025998</v>
+        <v>0.10812760515631625</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B9CB5E-E439-4FAB-8583-D6113BF49EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76576A6-5526-FC4B-B5F5-5BFAB687A0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,17 +4340,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.14</v>
+        <v>23.08</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,13 +4360,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11705.486828880001</v>
+        <v>11675.135523359999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,7 +4388,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4387,27 +4398,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4451,7 +4462,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4467,7 +4478,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4481,14 +4492,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10562766686379188</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.10662497056700704</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4507,7 +4518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4523,10 +4534,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4564,7 +4575,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4583,11 +4594,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4597,25 +4608,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4624,16 +4635,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4646,20 +4657,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4672,7 +4683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4685,16 +4696,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4707,16 +4718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4746,7 +4757,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4759,12 +4770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4777,16 +4788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4799,8 +4810,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4808,7 +4819,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4821,25 +4832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4865,23 +4876,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.7228216152731187E-2</v>
+        <v>5.7376989678258231E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5808124459809856E-2</v>
+        <v>4.5927209705372625E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4891,7 +4902,7 @@
         <v>0.80044648495694337</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4915,7 +4926,7 @@
         <v>0.15054731209829122</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4929,7 +4940,7 @@
         <v>0.12092451547494525</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4943,7 +4954,7 @@
         <v>0.70909055913759678</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4957,7 +4968,7 @@
         <v>1.7557268340491488</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4967,34 +4978,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5003,7 +5014,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5021,34 +5032,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5056,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5069,7 +5080,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5079,38 +5090,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5123,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5136,7 +5147,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>0.3857437197038544</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5154,12 +5165,12 @@
         <v>2.3913910654887354</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5185,7 +5196,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5198,12 +5209,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5216,7 +5227,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5229,16 +5240,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5251,7 +5262,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5264,7 +5275,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5274,16 +5285,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5322,7 +5333,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5344,7 +5355,7 @@
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5366,7 +5377,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5388,7 +5399,7 @@
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5410,7 +5421,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5423,16 +5434,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5442,30 +5453,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5474,16 +5485,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5496,7 +5507,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5509,26 +5520,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>1.829322250329541</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5538,7 +5549,7 @@
         <v>11.609618781212262</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5551,7 +5562,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5573,12 +5584,12 @@
         <v>0.51565717866448546</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5597,7 +5608,7 @@
         <v>2.279132885208865</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5607,7 +5618,7 @@
         <v>16.59052098499448</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5620,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5633,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5642,12 +5653,12 @@
         <v>0.31993291944146818</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5656,7 +5667,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5666,7 +5677,7 @@
         <v>2.8333926664293383</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5676,7 +5687,7 @@
         <v>23.296709554821966</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5689,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5702,7 +5713,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5711,12 +5722,12 @@
         <v>5.8264531266100761E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5735,7 +5746,7 @@
         <v>2.6975834619563113</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5745,7 +5756,7 @@
         <v>21.603471723847637</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5758,7 +5769,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5771,7 +5782,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5780,7 +5791,7 @@
         <v>0.12428977531548846</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5790,21 +5801,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5813,80 +5824,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5925,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5944,15 +5955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6001,7 +6012,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +6028,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6025,7 +6036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6072,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6097,7 +6108,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6133,7 +6144,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6169,7 +6180,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6205,7 +6216,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6221,7 +6232,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6237,7 +6248,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6253,7 +6264,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6283,7 +6294,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6313,7 +6324,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6349,7 +6360,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6385,7 +6396,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6421,13 +6432,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6443,7 +6454,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6459,7 +6470,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6475,7 +6486,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6511,7 +6522,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6547,7 +6558,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6583,7 +6594,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6603,7 +6614,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6611,7 +6622,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6648,7 +6659,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6685,7 +6696,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6722,7 +6733,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6759,7 +6770,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6796,7 +6807,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6812,12 +6823,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6866,7 +6877,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6915,7 +6926,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6964,7 +6975,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7013,7 +7024,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7062,7 +7073,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7111,7 +7122,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7160,7 +7171,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7209,7 +7220,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7258,7 +7269,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7307,7 +7318,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7356,7 +7367,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7405,7 +7416,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7454,12 +7465,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7508,7 +7519,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7557,12 +7568,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7611,7 +7622,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7660,7 +7671,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7709,7 +7720,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7758,13 +7769,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7813,7 +7824,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7862,7 +7873,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7911,7 +7922,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7960,7 +7971,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8009,12 +8020,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8064,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8113,7 +8124,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8163,7 +8174,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8212,7 +8223,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8262,7 +8273,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8278,13 +8289,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8333,7 +8344,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8367,7 +8378,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8401,7 +8412,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8450,7 +8461,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8531,18 +8542,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8558,7 +8569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8569,7 +8580,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8589,7 +8600,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8611,7 +8622,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8632,7 +8643,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8653,7 +8664,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8674,7 +8685,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8695,7 +8706,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8716,7 +8727,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8728,7 +8739,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8740,7 +8751,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8764,12 +8775,12 @@
         <v>4307827565.2530003</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8789,7 +8800,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8809,7 +8820,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8829,7 +8840,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8849,7 +8860,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8869,7 +8880,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8890,7 +8901,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8910,7 +8921,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8930,7 +8941,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8942,7 +8953,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8955,7 +8966,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8979,7 +8990,7 @@
         <v>407618191.44299996</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8996,7 +9007,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9015,7 +9026,7 @@
         <v>1794289725.1290007</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9030,7 +9041,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9049,7 +9060,7 @@
         <v>1792134939.4890006</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9065,7 +9076,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9082,7 +9093,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9102,7 +9113,7 @@
         <v>6123202173.5690002</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9113,7 +9124,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9126,7 +9137,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9145,7 +9156,7 @@
         <v>1407756416.8729999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9161,7 +9172,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9177,7 +9188,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9193,7 +9204,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9212,7 +9223,7 @@
         <v>133252792.61700001</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9232,7 +9243,7 @@
         <v>4715445756.6960001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9252,7 +9263,7 @@
         <v>4124860616.961</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9271,7 +9282,7 @@
         <v>590585139.73500001</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9282,7 +9293,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9296,7 +9307,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9310,7 +9321,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9325,10 +9336,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9341,7 +9352,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9355,7 +9366,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9366,10 +9377,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9381,7 +9392,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9395,7 +9406,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9409,10 +9420,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9424,7 +9435,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9435,7 +9446,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9446,10 +9457,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9461,7 +9472,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9477,7 +9488,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9488,7 +9499,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9502,7 +9513,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9518,7 +9529,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9528,7 +9539,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9538,7 +9549,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9548,7 +9559,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9558,10 +9569,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9573,7 +9584,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9589,7 +9600,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9605,7 +9616,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9618,7 +9629,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9631,10 +9642,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9646,7 +9657,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9660,7 +9671,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9674,7 +9685,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9688,7 +9699,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9702,7 +9713,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9713,7 +9724,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9721,7 +9732,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9738,7 +9749,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9755,7 +9766,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9772,7 +9783,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9803,19 +9814,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9872,7 +9883,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9895,7 +9906,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9909,7 +9920,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9966,7 +9977,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10021,7 +10032,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10076,7 +10087,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10131,7 +10142,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10188,7 +10199,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10243,7 +10254,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10298,7 +10309,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10355,7 +10366,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10410,7 +10421,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10465,7 +10476,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10520,7 +10531,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10577,7 +10588,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10634,7 +10645,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10660,7 +10671,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10685,7 +10696,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10742,7 +10753,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10761,7 +10772,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10784,7 +10795,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10805,7 +10816,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10862,7 +10873,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10919,7 +10930,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10976,18 +10987,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11046,7 +11057,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11106,7 +11117,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11161,18 +11172,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11229,7 +11240,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11288,7 +11299,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11345,18 +11356,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11414,7 +11425,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11472,7 +11483,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11527,18 +11538,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11596,10 +11607,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11622,14 +11633,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11684,7 +11695,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11739,7 +11750,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11796,7 +11807,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11851,11 +11862,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11865,7 +11876,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11892,7 +11903,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11919,7 +11930,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11974,11 +11985,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11988,7 +11999,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12043,7 +12054,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12098,7 +12109,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12153,7 +12164,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12208,7 +12219,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12264,7 +12275,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12319,11 +12330,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12333,7 +12344,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12358,7 +12369,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12383,7 +12394,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12408,7 +12419,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12435,10 +12446,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12461,7 +12472,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12482,7 +12493,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12539,7 +12550,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12596,7 +12607,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12653,7 +12664,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12710,7 +12721,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12767,7 +12778,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12826,7 +12837,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12883,7 +12894,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12940,7 +12951,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12997,7 +13008,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13054,7 +13065,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13112,7 +13123,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13169,7 +13180,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13195,7 +13206,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13219,7 +13230,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13276,18 +13287,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13343,7 +13354,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13399,7 +13410,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13454,19 +13465,19 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5808124459809856E-2</v>
+        <v>4.5927209705372625E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5808124459809856E-2</v>
+        <v>4.5927209705372625E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13509,11 +13520,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13534,7 +13545,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13591,7 +13602,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13648,10 +13659,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13674,7 +13685,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13684,7 +13695,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13741,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13798,7 +13809,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13855,7 +13866,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13912,7 +13923,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13969,11 +13980,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13996,7 +14007,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14053,7 +14064,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14110,7 +14121,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14137,18 +14148,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14200,7 +14211,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14252,11 +14263,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14310,7 +14321,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14365,7 +14376,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14419,7 +14430,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14475,7 +14486,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14532,7 +14543,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14551,7 +14562,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14574,7 +14585,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14595,7 +14606,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14653,795 +14664,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7228216152731187E-2</v>
+        <v>5.7376989678258231E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.4025756140978286E-2</v>
+        <v>5.4166204380512895E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9708193042651588E-2</v>
+        <v>4.9837417114686214E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.5285848807742311E-2</v>
+        <v>6.5455569385232115E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.0465728314977978E-2</v>
+        <v>6.0622918249938935E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5027817816921884E-2</v>
+        <v>5.5170871069478877E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8190655894268996E-2</v>
+        <v>3.8289938361931744E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.445665075958512E-2</v>
+        <v>2.4520229574384735E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0288463988876494E-2</v>
+        <v>2.0341206962851046E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.4034900394392145E-2</v>
+        <v>2.4097382804429562E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.5189295525285899E-2</v>
+        <v>2.5254778962526678E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2626465214804023E-2</v>
+        <v>7.2815268850544429E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8614902459110158E-2</v>
+        <v>6.8793277422175447E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3588365379726706E-2</v>
+        <v>8.3805666156277131E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9426412552630027E-2</v>
+        <v>7.9632893694447981E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8775172768873905E-2</v>
+        <v>6.8953964379191615E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1555058907169056E-2</v>
+        <v>5.1689084190289961E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7723370113112172E-2</v>
+        <v>3.7821437799714724E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7481730551037621E-2</v>
+        <v>2.7553173524740498E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0672429284545451E-2</v>
+        <v>3.0752166968994014E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1195083411574644E-2</v>
+        <v>3.1276179815590874E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15463,16 +15474,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15484,7 +15495,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15497,7 +15508,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15518,7 +15529,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15529,7 +15540,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15547,7 +15558,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15563,7 +15574,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15579,7 +15590,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15595,7 +15606,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15609,7 +15620,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15623,7 +15634,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15637,10 +15648,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15650,13 +15661,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15666,7 +15677,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15676,7 +15687,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15690,10 +15701,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15711,7 +15722,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15733,7 +15744,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15755,7 +15766,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15787,7 +15798,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15819,7 +15830,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15851,7 +15862,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15873,7 +15884,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15895,7 +15906,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15917,7 +15928,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15939,7 +15950,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15961,7 +15972,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15983,7 +15994,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16005,7 +16016,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16037,7 +16048,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16069,7 +16080,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16101,7 +16112,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16123,7 +16134,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16145,7 +16156,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16167,7 +16178,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16189,7 +16200,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16211,7 +16222,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16233,7 +16244,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16255,7 +16266,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16277,7 +16288,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16299,7 +16310,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16321,7 +16332,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16343,7 +16354,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16375,7 +16386,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16407,7 +16418,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16439,7 +16450,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16471,7 +16482,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16493,7 +16504,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16504,11 +16515,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16518,7 +16529,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>12125628782.891102</v>
@@ -16545,7 +16556,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16567,7 +16578,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16588,7 +16599,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16619,7 +16630,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16650,7 +16661,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16681,7 +16692,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16712,7 +16723,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16729,7 +16740,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16749,7 +16760,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16772,7 +16783,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16798,7 +16809,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16825,7 +16836,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16852,7 +16863,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16879,7 +16890,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16906,7 +16917,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16932,7 +16943,7 @@
         <v>51.93098214713887</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16958,7 +16969,7 @@
         <v>61.706101540668833</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16975,7 +16986,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16997,7 +17008,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17020,7 +17031,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17043,7 +17054,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17066,7 +17077,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17088,14 +17099,14 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17103,26 +17114,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17136,7 +17147,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17150,7 +17161,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17164,7 +17175,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17178,7 +17189,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17223,16 +17234,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17244,7 +17255,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17257,7 +17268,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17278,7 +17289,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17289,7 +17300,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17305,7 +17316,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17319,10 +17330,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17332,13 +17343,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17348,7 +17359,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17358,7 +17369,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17372,10 +17383,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17393,7 +17404,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17415,7 +17426,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17437,7 +17448,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17459,7 +17470,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17481,7 +17492,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17503,7 +17514,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17525,7 +17536,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17547,7 +17558,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17569,7 +17580,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17591,7 +17602,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17613,7 +17624,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17635,7 +17646,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17657,7 +17668,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17679,7 +17690,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17701,7 +17712,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17723,7 +17734,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17745,7 +17756,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17767,7 +17778,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17789,7 +17800,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17811,7 +17822,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17833,7 +17844,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17855,7 +17866,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17877,7 +17888,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17899,7 +17910,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17921,7 +17932,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17943,7 +17954,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17965,7 +17976,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17987,7 +17998,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18009,7 +18020,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18031,7 +18042,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18053,7 +18064,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18075,7 +18086,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18086,11 +18097,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18100,7 +18111,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>9705916937.1579227</v>
@@ -18127,7 +18138,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18149,7 +18160,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18170,7 +18181,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18191,7 +18202,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18212,7 +18223,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18233,7 +18244,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18254,14 +18265,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18271,7 +18282,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18294,7 +18305,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18320,7 +18331,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18347,7 +18358,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18374,7 +18385,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18401,7 +18412,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18428,7 +18439,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18454,7 +18465,7 @@
         <v>38.542642832299371</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18480,7 +18491,7 @@
         <v>46.3671027908849</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18497,7 +18508,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18519,7 +18530,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18542,7 +18553,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18565,7 +18576,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18588,7 +18599,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18610,14 +18621,14 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18625,23 +18636,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18671,17 +18682,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18694,7 +18705,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18703,10 +18714,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-23.08</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18726,7 +18737,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18735,7 +18746,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18755,7 +18766,7 @@
         <v>28.806753827145844</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18780,7 +18791,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18802,7 +18813,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18824,7 +18835,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18835,7 +18846,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18849,7 +18860,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18868,7 +18879,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18886,7 +18897,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18897,7 +18908,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18906,7 +18917,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18914,7 +18925,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18926,24 +18937,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.14</v>
+        <v>23.08</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18952,7 +18963,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18967,7 +18978,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18976,7 +18987,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18988,7 +18999,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -18999,7 +19010,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19014,7 +19025,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19025,7 +19036,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19034,7 +19045,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19046,7 +19057,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19057,7 +19068,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19072,7 +19083,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19083,7 +19094,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19092,7 +19103,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19104,7 +19115,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19115,7 +19126,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19130,7 +19141,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19142,7 +19153,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19155,7 +19166,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19164,12 +19175,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19179,12 +19190,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19193,7 +19204,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19205,7 +19216,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19216,7 +19227,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19231,7 +19242,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19242,7 +19253,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19251,7 +19262,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19263,7 +19274,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19274,7 +19285,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19289,7 +19300,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19300,7 +19311,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19320,7 +19331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19329,7 +19340,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19337,7 +19348,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19350,7 +19361,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19362,7 +19373,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19378,7 +19389,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19386,7 +19397,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19396,7 +19407,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19408,7 +19419,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19418,7 +19429,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19434,7 +19445,7 @@
         <v>0.13621601437445302</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19443,12 +19454,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19458,7 +19469,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19471,33 +19482,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19507,7 +19518,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19527,45 +19538,45 @@
         <v>0.51565717866448546</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.14</v>
+        <v>23.08</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10562766686379188</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.10662497056700704</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19574,7 +19585,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19586,7 +19597,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19596,7 +19607,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19616,14 +19627,14 @@
         <v>0.31993291944146818</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19634,7 +19645,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19646,7 +19657,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19658,7 +19669,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19677,15 +19688,15 @@
         <v>5.8264531266100761E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19694,7 +19705,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19704,7 +19715,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19714,7 +19725,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19733,16 +19744,16 @@
         <v>0.12428977531548846</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19750,7 +19761,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19758,7 +19769,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76576A6-5526-FC4B-B5F5-5BFAB687A0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1A756D-0FF8-4501-B830-8DB6F0A1BAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,17 +4329,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.08</v>
+        <v>23.35</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4360,13 +4349,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11675.135523359999</v>
+        <v>11811.7163982</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4398,27 +4387,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4433,7 +4422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4446,7 +4435,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4454,7 +4443,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4462,7 +4451,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4478,7 +4467,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4492,14 +4481,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10662497056700704</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.1021648112805309</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4518,7 +4507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4537,7 +4526,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4556,7 +4545,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4575,7 +4564,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4594,11 +4583,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4608,25 +4597,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4635,16 +4624,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4657,20 +4646,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4683,7 +4672,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4696,16 +4685,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4718,16 +4707,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4742,7 +4731,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4757,7 +4746,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4770,12 +4759,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4788,16 +4777,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4810,8 +4799,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,7 +4808,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4832,25 +4821,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4863,7 +4852,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4876,23 +4865,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.7376989678258231E-2</v>
+        <v>5.6713529840436816E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5927209705372625E-2</v>
+        <v>4.5396145610278375E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4902,7 +4891,7 @@
         <v>0.80044648495694337</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4913,7 +4902,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4926,7 +4915,7 @@
         <v>0.15054731209829122</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4940,7 +4929,7 @@
         <v>0.12092451547494525</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4954,7 +4943,7 @@
         <v>0.70909055913759678</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4968,7 +4957,7 @@
         <v>1.7557268340491488</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4978,34 +4967,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5014,7 +5003,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5023,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5032,34 +5021,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5080,7 +5069,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5090,38 +5079,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5134,7 +5123,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5147,7 +5136,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5156,7 +5145,7 @@
         <v>0.3857437197038544</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5165,12 +5154,12 @@
         <v>2.3913910654887354</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5183,7 +5172,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5196,7 +5185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5209,12 +5198,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5227,7 +5216,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5240,16 +5229,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5262,7 +5251,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5275,7 +5264,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5285,16 +5274,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5311,7 +5300,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5333,7 +5322,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5355,7 +5344,7 @@
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5377,7 +5366,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5399,7 +5388,7 @@
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5421,7 +5410,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5434,16 +5423,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5453,30 +5442,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5485,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5494,7 +5483,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5507,7 +5496,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5520,7 +5509,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5529,7 +5518,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5539,7 +5528,7 @@
         <v>1.829322250329541</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5549,7 +5538,7 @@
         <v>11.609618781212262</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5562,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5584,12 +5573,12 @@
         <v>0.51565717866448546</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5598,7 +5587,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5608,7 +5597,7 @@
         <v>2.279132885208865</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5618,7 +5607,7 @@
         <v>16.59052098499448</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5631,7 +5620,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5644,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5653,12 +5642,12 @@
         <v>0.31993291944146818</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5667,7 +5656,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5677,7 +5666,7 @@
         <v>2.8333926664293383</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5687,7 +5676,7 @@
         <v>23.296709554821966</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5700,7 +5689,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5713,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5722,12 +5711,12 @@
         <v>5.8264531266100761E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5736,7 +5725,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5746,7 +5735,7 @@
         <v>2.6975834619563113</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5756,7 +5745,7 @@
         <v>21.603471723847637</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5769,7 +5758,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5782,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5791,7 +5780,7 @@
         <v>0.12428977531548846</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5801,21 +5790,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5824,91 +5813,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5925,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5955,15 +5944,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6012,7 +6001,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6028,7 +6017,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6036,7 +6025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6072,7 +6061,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6108,7 +6097,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6144,7 +6133,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6180,7 +6169,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6216,7 +6205,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6232,7 +6221,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6248,7 +6237,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6264,7 +6253,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6294,7 +6283,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6324,7 +6313,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6360,7 +6349,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6396,7 +6385,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6432,13 +6421,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6454,7 +6443,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6470,7 +6459,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6486,7 +6475,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6522,7 +6511,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6558,7 +6547,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6594,7 +6583,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6614,7 +6603,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6622,7 +6611,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6659,7 +6648,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6696,7 +6685,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6733,7 +6722,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6770,7 +6759,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6807,7 +6796,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6823,12 +6812,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6877,7 +6866,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6926,7 +6915,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6975,7 +6964,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7024,7 +7013,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7073,7 +7062,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7122,7 +7111,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7171,7 +7160,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7220,7 +7209,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7269,7 +7258,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7318,7 +7307,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7367,7 +7356,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7416,7 +7405,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7465,12 +7454,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7519,7 +7508,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7568,12 +7557,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7622,7 +7611,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7671,7 +7660,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7720,7 +7709,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7769,13 +7758,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7824,7 +7813,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7873,7 +7862,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7922,7 +7911,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7971,7 +7960,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8020,12 +8009,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8075,7 +8064,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8124,7 +8113,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8174,7 +8163,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8223,7 +8212,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8273,7 +8262,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8289,13 +8278,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8344,7 +8333,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8378,7 +8367,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8412,7 +8401,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8461,7 +8450,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8542,7 +8531,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8553,7 +8542,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8569,7 +8558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8580,7 +8569,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8600,7 +8589,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8622,7 +8611,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8643,7 +8632,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8664,7 +8653,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8685,7 +8674,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8706,7 +8695,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8727,7 +8716,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8739,7 +8728,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8751,7 +8740,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8775,12 +8764,12 @@
         <v>4307827565.2530003</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8800,7 +8789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8820,7 +8809,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8840,7 +8829,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8860,7 +8849,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8880,7 +8869,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8901,7 +8890,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8921,7 +8910,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8941,7 +8930,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8953,7 +8942,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8966,7 +8955,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8990,7 +8979,7 @@
         <v>407618191.44299996</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9007,7 +8996,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9026,7 +9015,7 @@
         <v>1794289725.1290007</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9041,7 +9030,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9060,7 +9049,7 @@
         <v>1792134939.4890006</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9076,7 +9065,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9093,7 +9082,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9113,7 +9102,7 @@
         <v>6123202173.5690002</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9124,7 +9113,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9137,7 +9126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9156,7 +9145,7 @@
         <v>1407756416.8729999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9172,7 +9161,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9188,7 +9177,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9204,7 +9193,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9223,7 +9212,7 @@
         <v>133252792.61700001</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9243,7 +9232,7 @@
         <v>4715445756.6960001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9263,7 +9252,7 @@
         <v>4124860616.961</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9282,7 +9271,7 @@
         <v>590585139.73500001</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9293,7 +9282,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9307,7 +9296,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9321,7 +9310,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9336,10 +9325,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9352,7 +9341,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9366,7 +9355,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9377,10 +9366,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9392,7 +9381,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9406,7 +9395,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9420,10 +9409,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9435,7 +9424,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9446,7 +9435,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9457,10 +9446,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9472,7 +9461,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9488,7 +9477,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9499,7 +9488,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9513,7 +9502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9529,7 +9518,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9539,7 +9528,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9549,7 +9538,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9559,7 +9548,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9569,10 +9558,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9584,7 +9573,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9600,7 +9589,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9616,7 +9605,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9629,7 +9618,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9642,10 +9631,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9657,7 +9646,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9671,7 +9660,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9685,7 +9674,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9699,7 +9688,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9713,7 +9702,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9724,7 +9713,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9732,7 +9721,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9749,7 +9738,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9766,7 +9755,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9783,7 +9772,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9814,19 +9803,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9883,7 +9872,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9906,7 +9895,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9920,7 +9909,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9977,7 +9966,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10032,7 +10021,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10087,7 +10076,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10142,7 +10131,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10199,7 +10188,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10254,7 +10243,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10309,7 +10298,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10366,7 +10355,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10421,7 +10410,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10476,7 +10465,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10531,7 +10520,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10588,7 +10577,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10645,7 +10634,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10671,7 +10660,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10696,7 +10685,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10753,7 +10742,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10772,7 +10761,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10795,7 +10784,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10816,7 +10805,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10873,7 +10862,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10930,7 +10919,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10987,18 +10976,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11057,7 +11046,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11117,7 +11106,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11172,18 +11161,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11240,7 +11229,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11299,7 +11288,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11356,18 +11345,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11425,7 +11414,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11483,7 +11472,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11538,18 +11527,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11607,10 +11596,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11633,14 +11622,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11695,7 +11684,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11750,7 +11739,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11807,7 +11796,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11862,11 +11851,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11876,7 +11865,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11903,7 +11892,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11930,7 +11919,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11985,11 +11974,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11999,7 +11988,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12054,7 +12043,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12109,7 +12098,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12164,7 +12153,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12219,7 +12208,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12275,7 +12264,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12330,11 +12319,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12344,7 +12333,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12369,7 +12358,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12394,7 +12383,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12419,7 +12408,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12446,10 +12435,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12472,7 +12461,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12493,7 +12482,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12550,7 +12539,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12607,7 +12596,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12664,7 +12653,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12721,7 +12710,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12778,7 +12767,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12837,7 +12826,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12894,7 +12883,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12951,7 +12940,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13008,7 +12997,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13065,7 +13054,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13123,7 +13112,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13180,7 +13169,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13206,7 +13195,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13230,7 +13219,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13287,18 +13276,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13354,7 +13343,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13410,7 +13399,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13465,19 +13454,19 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5927209705372625E-2</v>
+        <v>4.5396145610278375E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5927209705372625E-2</v>
+        <v>4.5396145610278375E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13520,11 +13509,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13545,7 +13534,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13602,7 +13591,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13659,10 +13648,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13685,7 +13674,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13695,7 +13684,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13752,7 +13741,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13809,7 +13798,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13866,7 +13855,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13923,7 +13912,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13980,11 +13969,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14007,7 +13996,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14064,7 +14053,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14121,7 +14110,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14148,18 +14137,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14211,7 +14200,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14263,11 +14252,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14321,7 +14310,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14376,7 +14365,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14430,7 +14419,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14486,7 +14475,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14543,7 +14532,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14562,7 +14551,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14585,7 +14574,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14606,7 +14595,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14664,795 +14653,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7376989678258231E-2</v>
+        <v>5.6713529840436816E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.4166204380512895E-2</v>
+        <v>5.3539871396241431E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9837417114686214E-2</v>
+        <v>4.9261138629848295E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.5455569385232115E-2</v>
+        <v>6.4698695563646977E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.0622918249938935E-2</v>
+        <v>5.9921925190946058E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5170871069478877E-2</v>
+        <v>5.453292095432858E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8289938361931744E-2</v>
+        <v>3.7847185327339807E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4520229574384735E-2</v>
+        <v>2.4236698011854373E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0341206962851046E-2</v>
+        <v>2.0105998145721716E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.4097382804429562E-2</v>
+        <v>2.3818740690631016E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.5254778962526678E-2</v>
+        <v>2.496275368116127E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2815268850544429E-2</v>
+        <v>7.1973293579039185E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8793277422175447E-2</v>
+        <v>6.7997809117936153E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3805666156277131E-2</v>
+        <v>8.2836607061536449E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9632893694447981E-2</v>
+        <v>7.8712085073569971E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8953964379191615E-2</v>
+        <v>6.8156638024485752E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1689084190289961E-2</v>
+        <v>5.1091394565819785E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7821437799714724E-2</v>
+        <v>3.7384102116377542E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7553173524740498E-2</v>
+        <v>2.7234571518244564E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0752166968994014E-2</v>
+        <v>3.0396574460144828E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1276179815590874E-2</v>
+        <v>3.0914528057551918E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15474,16 +15463,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15495,7 +15484,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15508,7 +15497,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15529,7 +15518,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15540,7 +15529,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15558,7 +15547,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15574,7 +15563,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15590,7 +15579,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15606,7 +15595,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15620,7 +15609,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15634,7 +15623,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15648,10 +15637,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15661,13 +15650,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15677,7 +15666,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15687,7 +15676,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15701,10 +15690,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15722,7 +15711,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15744,7 +15733,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15766,7 +15755,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15798,7 +15787,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15830,7 +15819,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15862,7 +15851,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15884,7 +15873,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15906,7 +15895,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15928,7 +15917,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15950,7 +15939,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15972,7 +15961,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15994,7 +15983,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16016,7 +16005,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16048,7 +16037,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16080,7 +16069,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16112,7 +16101,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16134,7 +16123,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16156,7 +16145,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16178,7 +16167,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16200,7 +16189,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16222,7 +16211,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16244,7 +16233,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16266,7 +16255,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16288,7 +16277,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16310,7 +16299,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16332,7 +16321,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16354,7 +16343,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16386,7 +16375,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16418,7 +16407,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16450,7 +16439,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16482,7 +16471,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16504,7 +16493,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16515,11 +16504,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16529,7 +16518,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>12125628782.891102</v>
@@ -16556,7 +16545,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16578,7 +16567,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16599,7 +16588,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16630,7 +16619,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16661,7 +16650,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16692,7 +16681,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16723,7 +16712,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16740,7 +16729,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16760,7 +16749,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16783,7 +16772,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16809,7 +16798,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16836,7 +16825,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16863,7 +16852,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16890,7 +16879,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16917,7 +16906,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16943,7 +16932,7 @@
         <v>51.93098214713887</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16969,7 +16958,7 @@
         <v>61.706101540668833</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16986,7 +16975,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17008,7 +16997,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17031,7 +17020,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17054,7 +17043,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17077,7 +17066,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17099,14 +17088,14 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17114,26 +17103,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17147,7 +17136,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17161,7 +17150,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17175,7 +17164,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17189,7 +17178,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17234,16 +17223,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17255,7 +17244,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17268,7 +17257,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17289,7 +17278,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17300,7 +17289,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17316,7 +17305,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17330,10 +17319,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17343,13 +17332,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17359,7 +17348,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17369,7 +17358,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17383,10 +17372,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17404,7 +17393,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17426,7 +17415,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17448,7 +17437,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17470,7 +17459,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17492,7 +17481,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17514,7 +17503,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17536,7 +17525,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17558,7 +17547,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17580,7 +17569,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17602,7 +17591,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17624,7 +17613,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17646,7 +17635,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17668,7 +17657,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17690,7 +17679,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17712,7 +17701,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17734,7 +17723,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17756,7 +17745,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17778,7 +17767,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17800,7 +17789,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17822,7 +17811,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17844,7 +17833,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17866,7 +17855,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17888,7 +17877,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17910,7 +17899,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17932,7 +17921,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17954,7 +17943,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17976,7 +17965,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17998,7 +17987,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18020,7 +18009,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18042,7 +18031,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18064,7 +18053,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18086,7 +18075,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18097,11 +18086,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18111,7 +18100,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>9705916937.1579227</v>
@@ -18138,7 +18127,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18160,7 +18149,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18181,7 +18170,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18202,7 +18191,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18223,7 +18212,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18244,7 +18233,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18265,14 +18254,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18282,7 +18271,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18305,7 +18294,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18331,7 +18320,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18358,7 +18347,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18385,7 +18374,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18412,7 +18401,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18439,7 +18428,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18465,7 +18454,7 @@
         <v>38.542642832299371</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18491,7 +18480,7 @@
         <v>46.3671027908849</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18508,7 +18497,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18530,7 +18519,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18553,7 +18542,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18576,7 +18565,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18599,7 +18588,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18621,14 +18610,14 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18636,23 +18625,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18682,7 +18671,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18692,7 +18681,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18705,7 +18694,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18714,10 +18703,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.08</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-23.35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18737,7 +18726,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18746,7 +18735,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18766,7 +18755,7 @@
         <v>28.806753827145844</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18791,7 +18780,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18813,7 +18802,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18835,7 +18824,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18846,7 +18835,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18860,7 +18849,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18879,7 +18868,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18897,7 +18886,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18908,7 +18897,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18917,7 +18906,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18925,7 +18914,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18937,24 +18926,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.08</v>
+        <v>23.35</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18963,7 +18952,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18978,7 +18967,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18987,7 +18976,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18999,7 +18988,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19010,7 +18999,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19025,7 +19014,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19036,7 +19025,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19045,7 +19034,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19057,7 +19046,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19068,7 +19057,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19083,7 +19072,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19094,7 +19083,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19103,7 +19092,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19115,7 +19104,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19126,7 +19115,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19141,7 +19130,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19153,7 +19142,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19166,7 +19155,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19175,12 +19164,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19190,12 +19179,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19204,7 +19193,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19216,7 +19205,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19227,7 +19216,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19242,7 +19231,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19253,7 +19242,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19262,7 +19251,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19274,7 +19263,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19285,7 +19274,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19300,7 +19289,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19311,7 +19300,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19331,7 +19320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19340,7 +19329,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19348,7 +19337,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19361,7 +19350,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19373,7 +19362,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19389,7 +19378,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19397,7 +19386,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19407,7 +19396,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19419,7 +19408,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19429,7 +19418,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19445,7 +19434,7 @@
         <v>0.13621601437445302</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19454,12 +19443,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19469,7 +19458,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19482,12 +19471,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19496,7 +19485,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19508,7 +19497,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19518,7 +19507,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19538,45 +19527,45 @@
         <v>0.51565717866448546</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.08</v>
+        <v>23.35</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10662497056700704</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.1021648112805309</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19585,7 +19574,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19597,7 +19586,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19607,7 +19596,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19627,14 +19616,14 @@
         <v>0.31993291944146818</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19645,7 +19634,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19657,7 +19646,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19669,7 +19658,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19688,15 +19677,15 @@
         <v>5.8264531266100761E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19705,7 +19694,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19715,7 +19704,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19725,7 +19714,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19744,16 +19733,16 @@
         <v>0.12428977531548846</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19761,7 +19750,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19769,7 +19758,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1A756D-0FF8-4501-B830-8DB6F0A1BAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A1BC43-0030-4E1B-8F95-E4D25D5FBA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.35</v>
+        <v>23.32</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11811.7163982</v>
+        <v>11796.540745440001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1021648112805309</v>
+        <v>0.10265688775118464</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.6713529840436816E-2</v>
+        <v>5.6786488926852473E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5396145610278375E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5396145610278375E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5396145610278375E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14660,50 +14660,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6713529840436816E-2</v>
+        <v>5.6786488926852473E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3539871396241431E-2</v>
+        <v>5.3608747731656844E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9261138629848295E-2</v>
+        <v>4.9324510592065079E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.4698695563646977E-2</v>
+        <v>6.4781927161713423E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>5.9921925190946058E-2</v>
+        <v>5.9999011715634237E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.453292095432858E-2</v>
+        <v>5.4603074797751817E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7847185327339807E-2</v>
+        <v>3.7895873816182875E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4236698011854373E-2</v>
+        <v>2.4267877297461393E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0105998145721716E-2</v>
+        <v>2.0131863494965783E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3818740690631016E-2</v>
+        <v>2.3849382295293063E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.496275368116127E-2</v>
+        <v>2.4994867000648187E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14717,43 +14717,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1973293579039185E-2</v>
+        <v>7.2065883579355283E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7997809117936153E-2</v>
+        <v>6.8085284858653908E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2836607061536449E-2</v>
+        <v>8.2943172164960374E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8712085073569971E-2</v>
+        <v>7.8813344188158621E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8156638024485752E-2</v>
+        <v>6.8244318090554978E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1091394565819785E-2</v>
+        <v>5.1157121059686624E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7384102116377542E-2</v>
+        <v>3.7432194872101872E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7234571518244564E-2</v>
+        <v>2.7269607416424122E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0396574460144828E-2</v>
+        <v>3.043567811511071E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0914528057551918E-2</v>
+        <v>3.0954298033612233E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.35</v>
+        <v>-23.32</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.35</v>
+        <v>23.32</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.35</v>
+        <v>23.32</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1021648112805309</v>
+        <v>0.10265688775118464</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A1BC43-0030-4E1B-8F95-E4D25D5FBA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A39699A-3712-4499-A95C-EAE4B9F52817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.32</v>
+        <v>23.11</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11796.540745440001</v>
+        <v>11690.31117612</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10265688775118464</v>
+        <v>0.10612587528562245</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.6786488926852473E-2</v>
+        <v>5.7302506351112066E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5867589787970578E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5867589787970578E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5867589787970578E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14660,50 +14660,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6786488926852473E-2</v>
+        <v>5.7302506351112066E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3608747731656844E-2</v>
+        <v>5.409588910005355E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9324510592065079E-2</v>
+        <v>4.9772721203243518E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.4781927161713423E-2</v>
+        <v>6.5370598936008537E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>5.9999011715634237E-2</v>
+        <v>6.0544221255239748E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4603074797751817E-2</v>
+        <v>5.5099251591673407E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7895873816182875E-2</v>
+        <v>3.8240232686862163E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4267877297461393E-2</v>
+        <v>2.4488398899904791E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0131863494965783E-2</v>
+        <v>2.0314801241999227E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3849382295293063E-2</v>
+        <v>2.4066101043973789E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.4994867000648187E-2</v>
+        <v>2.5221994740593497E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14717,43 +14717,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2065883579355283E-2</v>
+        <v>7.2720744485961289E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8085284858653908E-2</v>
+        <v>6.8703974162864972E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2943172164960374E-2</v>
+        <v>8.3696874724659295E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8813344188158621E-2</v>
+        <v>7.952951910289309E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8244318090554978E-2</v>
+        <v>6.8864452525821823E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1157121059686624E-2</v>
+        <v>5.1621984556983656E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7432194872101872E-2</v>
+        <v>3.7772340303652785E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7269607416424122E-2</v>
+        <v>2.7517405666421923E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.043567811511071E-2</v>
+        <v>3.0712246371457457E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0954298033612233E-2</v>
+        <v>3.1235578976366828E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.32</v>
+        <v>-23.11</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.32</v>
+        <v>23.11</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.32</v>
+        <v>23.11</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10265688775118464</v>
+        <v>0.10612587528562245</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A39699A-3712-4499-A95C-EAE4B9F52817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EC2442-B472-421C-B949-99E725FDEE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EC2442-B472-421C-B949-99E725FDEE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E932DC7A-B441-4EE7-8569-7E5F01C3F156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.11</v>
+        <v>23.14</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11690.31117612</v>
+        <v>11705.486828880001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10612587528562245</v>
+        <v>0.10562766686379188</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.7302506351112066E-2</v>
+        <v>5.7228216152731187E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5867589787970578E-2</v>
+        <v>4.5808124459809856E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5867589787970578E-2</v>
+        <v>4.5808124459809856E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5867589787970578E-2</v>
+        <v>4.5808124459809856E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14660,50 +14660,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7302506351112066E-2</v>
+        <v>5.7228216152731187E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.409588910005355E-2</v>
+        <v>5.4025756140978286E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9772721203243518E-2</v>
+        <v>4.9708193042651588E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.5370598936008537E-2</v>
+        <v>6.5285848807742311E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.0544221255239748E-2</v>
+        <v>6.0465728314977978E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5099251591673407E-2</v>
+        <v>5.5027817816921884E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8240232686862163E-2</v>
+        <v>3.8190655894268996E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4488398899904791E-2</v>
+        <v>2.445665075958512E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0314801241999227E-2</v>
+        <v>2.0288463988876494E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.4066101043973789E-2</v>
+        <v>2.4034900394392145E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.5221994740593497E-2</v>
+        <v>2.5189295525285899E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14717,43 +14717,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2720744485961289E-2</v>
+        <v>7.2626465214804023E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8703974162864972E-2</v>
+        <v>6.8614902459110158E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3696874724659295E-2</v>
+        <v>8.3588365379726706E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.952951910289309E-2</v>
+        <v>7.9426412552630027E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8864452525821823E-2</v>
+        <v>6.8775172768873905E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1621984556983656E-2</v>
+        <v>5.1555058907169056E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7772340303652785E-2</v>
+        <v>3.7723370113112172E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7517405666421923E-2</v>
+        <v>2.7481730551037621E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0712246371457457E-2</v>
+        <v>3.0672429284545451E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1235578976366828E-2</v>
+        <v>3.1195083411574644E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.11</v>
+        <v>-23.14</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.11</v>
+        <v>23.14</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.11</v>
+        <v>23.14</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10612587528562245</v>
+        <v>0.10562766686379188</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E932DC7A-B441-4EE7-8569-7E5F01C3F156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6316EC78-C994-4725-A2CE-7253C789B509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.14</v>
+        <v>23.58</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11705.486828880001</v>
+        <v>11928.063069359998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10562766686379188</v>
+        <v>9.8420776996342108E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.7228216152731187E-2</v>
+        <v>5.6160344434868531E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5808124459809856E-2</v>
+        <v>4.4953350296861753E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5808124459809856E-2</v>
+        <v>4.4953350296861753E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5808124459809856E-2</v>
+        <v>4.4953350296861753E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14660,50 +14660,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7228216152731187E-2</v>
+        <v>5.6160344434868531E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.4025756140978286E-2</v>
+        <v>5.3017641946659783E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9708193042651588E-2</v>
+        <v>4.8780644063060125E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.5285848807742311E-2</v>
+        <v>6.4067622621338305E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.0465728314977978E-2</v>
+        <v>5.9337445004605201E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5027817816921884E-2</v>
+        <v>5.4001005270719785E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8190655894268996E-2</v>
+        <v>3.7478022790219875E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.445665075958512E-2</v>
+        <v>2.4000292560508892E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0288463988876494E-2</v>
+        <v>1.990988365999161E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.4034900394392145E-2</v>
+        <v>2.3586412007049799E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.5189295525285899E-2</v>
+        <v>2.4719266261879379E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14717,43 +14717,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2626465214804023E-2</v>
+        <v>7.1271263997903539E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8614902459110158E-2</v>
+        <v>6.7334556526879114E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3588365379726706E-2</v>
+        <v>8.2028616407416294E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9426412552630027E-2</v>
+        <v>7.7944325125863412E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8775172768873905E-2</v>
+        <v>6.7491836211693912E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1555058907169056E-2</v>
+        <v>5.0593047629851243E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7723370113112172E-2</v>
+        <v>3.7019456506251734E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7481730551037621E-2</v>
+        <v>2.6968924722265083E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0672429284545451E-2</v>
+        <v>3.0100085396284219E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1195083411574644E-2</v>
+        <v>3.0612986859365452E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.14</v>
+        <v>-23.58</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.14</v>
+        <v>23.58</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.14</v>
+        <v>23.58</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10562766686379188</v>
+        <v>9.8420776996342108E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6316EC78-C994-4725-A2CE-7253C789B509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79F0C70-F318-46D4-804F-7DC0BEDE2BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.58</v>
+        <v>23.46</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11928.063069359998</v>
+        <v>11867.360458319999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.8420776996342108E-2</v>
+        <v>0.10036791365456454</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.6160344434868531E-2</v>
+        <v>5.6447609623793686E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.4953350296861753E-2</v>
+        <v>4.5183290707587385E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.4953350296861753E-2</v>
+        <v>4.5183290707587385E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.4953350296861753E-2</v>
+        <v>4.5183290707587385E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14660,50 +14660,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6160344434868531E-2</v>
+        <v>5.6447609623793686E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3017641946659783E-2</v>
+        <v>5.3288831931041669E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.8780644063060125E-2</v>
+        <v>4.9030161423996493E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.4067622621338305E-2</v>
+        <v>6.4395334245999872E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>5.9337445004605201E-2</v>
+        <v>5.9640961347339747E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4001005270719785E-2</v>
+        <v>5.4277225246529087E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7478022790219875E-2</v>
+        <v>3.7669726231602071E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4000292560508892E-2</v>
+        <v>2.4123056205319678E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.990988365999161E-2</v>
+        <v>2.0011724497127112E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3586412007049799E-2</v>
+        <v>2.3707058615781512E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.4719266261879379E-2</v>
+        <v>2.4845707521530931E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14717,43 +14717,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1271263997903539E-2</v>
+        <v>7.1635822893033468E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7334556526879114E-2</v>
+        <v>6.7678978810904067E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2028616407416294E-2</v>
+        <v>8.2448200123055246E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7944325125863412E-2</v>
+        <v>7.8343017325995704E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7491836211693912E-2</v>
+        <v>6.783706299538543E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0593047629851243E-2</v>
+        <v>5.0851835597267359E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7019456506251734E-2</v>
+        <v>3.7208814340043299E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6968924722265083E-2</v>
+        <v>2.7106873186317586E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0100085396284219E-2</v>
+        <v>3.0254050027467255E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0612986859365452E-2</v>
+        <v>3.0769575027444047E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.58</v>
+        <v>-23.46</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.58</v>
+        <v>23.46</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.58</v>
+        <v>23.46</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.8420776996342108E-2</v>
+        <v>0.10036791365456454</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79F0C70-F318-46D4-804F-7DC0BEDE2BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C442BE-3EB6-4DC6-ADAB-BCB1E7C9820C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11867.360458319999</v>
+        <v>11847.126254640001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10036791365456454</v>
+        <v>0.10101999321043009</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.6447609623793686E-2</v>
+        <v>5.6544018863116975E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5183290707587385E-2</v>
+        <v>4.5260461144321092E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5183290707587385E-2</v>
+        <v>4.5260461144321092E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5183290707587385E-2</v>
+        <v>4.5260461144321092E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14660,50 +14660,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6447609623793686E-2</v>
+        <v>5.6544018863116975E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3288831931041669E-2</v>
+        <v>5.3379846161496047E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9030161423996493E-2</v>
+        <v>4.9113902092525946E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.4395334245999872E-2</v>
+        <v>6.4505317737453327E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>5.9640961347339747E-2</v>
+        <v>5.9742824645968848E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4277225246529087E-2</v>
+        <v>5.43699275953703E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7669726231602071E-2</v>
+        <v>3.7734063936523676E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4123056205319678E-2</v>
+        <v>2.4164256984491872E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0011724497127112E-2</v>
+        <v>2.0045903360486853E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3707058615781512E-2</v>
+        <v>2.3747548895227764E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.4845707521530931E-2</v>
+        <v>2.4888142547186833E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14717,43 +14717,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1635822893033468E-2</v>
+        <v>7.1758172718640684E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7678978810904067E-2</v>
+        <v>6.779457057659305E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2448200123055246E-2</v>
+        <v>8.258901686109632E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8343017325995704E-2</v>
+        <v>7.8476822650207473E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.783706299538543E-2</v>
+        <v>6.7952924759681566E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0851835597267359E-2</v>
+        <v>5.0938687579500083E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7208814340043299E-2</v>
+        <v>3.7272364834219286E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7106873186317586E-2</v>
+        <v>2.7153170151622993E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0254050027467255E-2</v>
+        <v>3.0305722188060706E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0769575027444047E-2</v>
+        <v>3.0822127674800907E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.46</v>
+        <v>-23.42</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10036791365456454</v>
+        <v>0.10101999321043009</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C442BE-3EB6-4DC6-ADAB-BCB1E7C9820C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292755A3-10B2-4E49-9211-6DB68030B845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.42</v>
+        <v>23.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11847.126254640001</v>
+        <v>11973.590027640001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10101999321043009</v>
+        <v>9.6969308965579426E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.6544018863116975E-2</v>
+        <v>5.5946807003557232E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5260461144321092E-2</v>
+        <v>4.4782425010561892E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5260461144321092E-2</v>
+        <v>4.4782425010561892E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5260461144321092E-2</v>
+        <v>4.4782425010561892E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14660,50 +14660,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6544018863116975E-2</v>
+        <v>5.5946807003557232E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3379846161496047E-2</v>
+        <v>5.2816053954467153E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9113902092525946E-2</v>
+        <v>4.8595166328980047E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>6.4505317737453327E-2</v>
+        <v>6.3824019493500514E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>5.9742824645968848E-2</v>
+        <v>5.9111827342990725E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.43699275953703E-2</v>
+        <v>5.3795678254481297E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7734063936523676E-2</v>
+        <v>3.733552080242436E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.4164256984491872E-2</v>
+        <v>2.3909036695259806E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0045903360486853E-2</v>
+        <v>1.983418068029582E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3747548895227764E-2</v>
+        <v>2.3496729832118049E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.4888142547186833E-2</v>
+        <v>2.4625276656320898E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14717,43 +14717,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1758172718640684E-2</v>
+        <v>7.100027059867195E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.779457057659305E-2</v>
+        <v>6.7078531597119101E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.258901686109632E-2</v>
+        <v>8.1716720527540171E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8476822650207473E-2</v>
+        <v>7.7647958870631972E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7952924759681566E-2</v>
+        <v>6.723521326031863E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0938687579500083E-2</v>
+        <v>5.0400678627456355E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7272364834219286E-2</v>
+        <v>3.6878698116494114E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7153170151622993E-2</v>
+        <v>2.6866381282256466E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0305722188060706E-2</v>
+        <v>2.9985636402381988E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0822127674800907E-2</v>
+        <v>3.0496587669786111E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.42</v>
+        <v>-23.67</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.42</v>
+        <v>23.67</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.42</v>
+        <v>23.67</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10101999321043009</v>
+        <v>9.6969308965579426E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292755A3-10B2-4E49-9211-6DB68030B845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F11C926-F602-4890-8B9F-41C5C2211925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -2470,9 +2471,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3149,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3894,6 +3892,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4223,10 +4225,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4238,18 +4240,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4263,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4272,10 +4274,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4289,7 +4291,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4299,7 +4301,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4312,20 +4314,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4341,17 +4343,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4365,7 +4367,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4391,35 +4393,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4427,7 +4429,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4437,26 +4439,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4477,11 +4479,11 @@
         <v>27.746753827145845</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.6969308965579426E-2</v>
+        <v>9.2706938820872553E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4490,7 +4492,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4501,7 +4503,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4509,37 +4511,37 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>13.438941031541804</v>
+        <v>13.256008806508849</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>18.869653870203344</v>
+        <v>18.641740581682459</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4547,18 +4549,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>26.130102221251306</v>
+        <v>25.846762954608369</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4566,18 +4568,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>24.301055185803946</v>
+        <v>24.031296839608316</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4589,7 +4591,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4597,45 +4599,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4650,18 +4652,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4674,7 +4676,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4686,17 +4688,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4708,17 +4710,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4733,7 +4735,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4748,7 +4750,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4761,12 +4763,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4778,17 +4780,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4800,17 +4802,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4821,27 +4823,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4854,7 +4856,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4867,24 +4869,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>5.5946807003557232E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
-        <v>4.4782425010561892E-2</v>
+        <f>Normalized_FCF!C94</f>
+        <v>4.0304182509505702E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4893,73 +4895,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>0.15648173464349882</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.15054731209829122</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>0.13375671427886937</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.12092451547494525</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.66633267926556194</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.70909055913759678</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.7557268340491488</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.7557268340491488</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4970,33 +4972,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5005,7 +5007,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5014,7 +5016,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5026,31 +5028,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5058,7 +5060,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5071,7 +5073,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5083,36 +5085,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5125,7 +5127,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5138,7 +5140,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5147,7 +5149,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5156,12 +5158,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5174,7 +5176,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5187,7 +5189,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5200,12 +5202,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5218,7 +5220,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5229,18 +5231,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5253,7 +5255,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5266,7 +5268,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5274,30 +5276,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5412,7 +5414,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5423,18 +5425,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5443,31 +5445,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5476,20 +5478,20 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.06</v>
+        <v>0.95400000000000007</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5498,7 +5500,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5511,11 +5513,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5525,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.829322250329541</v>
+        <v>1.6463900252965866</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5540,11 +5542,11 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>13.438941031541804</v>
+        <v>13.256008806508849</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5553,7 +5555,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5566,21 +5568,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51565717866448546</v>
+        <v>0.5222501021528535</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5594,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.279132885208865</v>
+        <v>2.0512195966879787</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5609,11 +5611,11 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>18.869653870203344</v>
+        <v>18.641740581682459</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5622,7 +5624,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5635,21 +5637,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31993291944146818</v>
+        <v>0.32814697179298713</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5663,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.8333926664293383</v>
+        <v>2.5500533997864046</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5678,11 +5680,11 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>26.130102221251306</v>
+        <v>25.846762954608369</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5691,7 +5693,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5704,21 +5706,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>5.8264531266100761E-2</v>
+        <v>6.8476149836260602E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5732,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>2.6975834619563113</v>
+        <v>2.4278251157606801</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5747,11 +5749,11 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>24.301055185803946</v>
+        <v>24.031296839608316</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5760,7 +5762,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5773,16 +5775,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.12428977531548846</v>
+        <v>0.13401075821731312</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5791,98 +5793,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5920,7 +5922,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5944,12 +5946,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6207,7 +6209,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6223,7 +6225,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6239,7 +6241,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6477,7 +6479,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>1038904494</v>
@@ -6513,7 +6515,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-581740675</v>
@@ -6549,7 +6551,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-435769097</v>
@@ -6608,7 +6610,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6761,7 +6763,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7162,7 +7164,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7211,7 +7213,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7559,12 +7561,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7613,7 +7615,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7662,7 +7664,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7711,7 +7713,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7913,7 +7915,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8165,7 +8167,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8531,15 +8533,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8560,7 +8562,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8571,19 +8573,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8644,7 +8646,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8665,7 +8667,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>304944913.81999999</v>
@@ -8676,7 +8678,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8686,7 +8688,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8707,7 +8709,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8771,19 +8773,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8791,7 +8793,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8820,7 +8822,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8840,7 +8842,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>664145486.29999995</v>
@@ -8851,7 +8853,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8860,7 +8862,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8881,7 +8883,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>91308996.629999995</v>
@@ -8901,7 +8903,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8921,7 +8923,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8981,16 +8983,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9023,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>2154785.64</v>
@@ -9067,7 +9069,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9117,10 +9119,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9128,10 +9130,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9153,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9169,7 +9171,7 @@
         <v>2885347.22</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9185,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9214,14 +9216,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>1359592631.5</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9241,7 +9243,7 @@
         <v>86283945.589999914</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9260,7 +9262,7 @@
         <v>1445876577.0899999</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9284,13 +9286,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9298,7 +9300,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9330,7 +9332,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9357,7 +9359,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9371,7 +9373,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9383,7 +9385,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9397,7 +9399,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9414,7 +9416,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9451,10 +9453,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9463,7 +9465,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9474,12 +9476,12 @@
         <v>3.7631672027541312E-4</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9490,13 +9492,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9504,7 +9506,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9515,12 +9517,12 @@
         <v>3530916331.352602</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9530,7 +9532,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9540,7 +9542,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9550,7 +9552,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9563,7 +9565,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9575,7 +9577,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9586,12 +9588,12 @@
         <v>-526131065.96869904</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9602,12 +9604,12 @@
         <v>8.7110964543626963</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9615,12 +9617,12 @@
         <v>1052262131.9373981</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9628,7 +9630,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9636,10 +9638,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9648,7 +9650,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9662,7 +9664,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9676,7 +9678,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9690,7 +9692,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9704,7 +9706,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9715,15 +9717,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9740,7 +9742,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9757,7 +9759,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9774,7 +9776,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9802,17 +9804,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10134,7 +10136,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10301,7 +10303,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10413,7 +10415,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10523,7 +10525,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10580,7 +10582,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10645,7 +10647,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10670,7 +10672,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10764,7 +10766,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -10983,7 +10985,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -10998,7 +11000,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11058,7 +11060,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11175,14 +11177,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-301299427</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11240,7 +11242,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11352,7 +11354,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11534,21 +11536,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11602,7 +11604,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11687,7 +11689,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11742,7 +11744,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11858,11 +11860,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11875,7 +11877,7 @@
         <v>3.0451386547102714E-2</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11902,7 +11904,7 @@
         <v>2.7005899779057908E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11981,17 +11983,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12046,7 +12048,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12101,7 +12103,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12156,7 +12158,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12211,13 +12213,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12267,7 +12269,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12326,17 +12328,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12361,7 +12363,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12386,7 +12388,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12411,7 +12413,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12441,12 +12443,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>464</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12464,7 +12466,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12656,7 +12658,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12829,7 +12831,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12943,7 +12945,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13115,7 +13117,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13222,7 +13224,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13283,7 +13285,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13402,7 +13404,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13457,1310 +13459,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>4.4782425010561892E-2</v>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0.1</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.4782425010561892E-2</v>
-      </c>
-      <c r="H93" s="23">
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>4.0304182509505702E-2</v>
+      </c>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>4.0304182509505702E-2</v>
+      </c>
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I93" s="23">
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="J93" s="23">
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-6.0299603937806423E-2</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>4.7862862106057502E-2</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>-1.1293593562295867E-2</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.15009778924884709</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.13153374724222933</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>9.3452176674909682E-2</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.15253747570768272</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.16495991847911595</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>2.5541139949896152E-2</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>6.0892957146166049E-2</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>3.9418987044637754E-2</v>
+        <f>C4/G4-1</f>
+        <v>-6.0299603937806423E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>4.7862862106057502E-2</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>-1.1293593562295867E-2</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.15009778924884709</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.13153374724222933</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>9.3452176674909682E-2</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.15253747570768272</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.16495991847911595</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>2.5541139949896152E-2</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>6.0892957146166049E-2</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>3.9418987044637754E-2</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>0.11475267321445082</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>-0.23318827735973335</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>0.11340845482813555</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>8.3522861922076697E-2</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>0.37191828149447903</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>0.43070283050659341</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>0.27020181746958882</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>-0.15619773728622377</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>-1.8902279872139549E-2</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>10057056869.68</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>10057056869.68</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>9398773153</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>8547307801</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>8072221913</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>6978984597</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>5408704521</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>5128131468</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>4673876647</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>4220141265</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>4580811369</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>488915470.69999999</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>422673488</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>456344428</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>319728461</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>217535243</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>224562135</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>1545872989.1700001</v>
+        <f>BS!C4</f>
+        <v>488915470.69999999</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>422673488</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>456344428</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>319728461</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>217535243</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>224562135</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>1545872989.1700001</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>1623301115</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>984697312</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1462249097</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1687299780</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>1389523101</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>4328912448.4399996</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>4328912448.4399996</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>3866253573</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>3275808581</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>3276083890</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>2771099894</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>1753709637</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>1768910685</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>1542190319</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>1188658961</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>1649560528</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>5728144421.2400007</v>
+        <f>BS!G30</f>
+        <v>4328912448.4399996</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>4328912448.4399996</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>3866253573</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>3275808581</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>3276083890</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>2771099894</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>1753709637</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>1768910685</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>1542190319</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>1188658961</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>1649560528</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>5728144421.2400007</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>5728144421.2400007</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>5532519580</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>5271499220</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>4796138023</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>4207884703</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>3654994884</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>3359220783</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>3131686328</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>3031482304</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>2931250841</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>7.295780523371137E-2</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>5.9269654910014027E-2</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>6.7053984782289452E-2</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>4.6449440257565366E-2</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>3.6346582594112269E-2</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>4.2455894551949612E-2</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0.23068098110792726</v>
+        <v>7.295780523371137E-2</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>0.22762841681021401</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>5.9269654910014027E-2</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.14468869240583634</v>
+        <f t="shared" si="43"/>
+        <v>6.7053984782289452E-2</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.21243229914643227</v>
+        <f t="shared" si="43"/>
+        <v>4.6449440257565366E-2</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.28192020736059514</v>
+        <f t="shared" si="43"/>
+        <v>3.6346582594112269E-2</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.26270433460901155</v>
+        <f t="shared" si="43"/>
+        <v>4.2455894551949612E-2</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>0.23068098110792726</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>0.22762841681021401</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.14468869240583634</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.21243229914643227</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.28192020736059514</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.26270433460901155</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.2220563640870079</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>0.5220279107320227</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>1.5660017367806311</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>1.4464739656204468</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>0.74139088985897428</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>1.0709352013930644</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>1.6912837855630598</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>0.91058543593464991</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>1.315617423655931</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>0.73045375218197883</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.2220563640870079</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>0.5220279107320227</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>1.5660017367806311</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>1.4464739656204468</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>0.74139088985897428</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>1.0709352013930644</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>1.6912837855630598</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>0.91058543593464991</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>1.315617423655931</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>0.73045375218197883</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.6428022550076953</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>0.72058330796850312</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.0050214211779154</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.9000554717795306</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.92660927803755555</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.445697281199763</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>2.6087351386041981</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.2334331277013026</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.6789411119014945</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.90461306092266658</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>0.13375671427886937</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.12092451547494525</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.11366854005290915</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.14656115763824204</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.1513906802652335</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.15809879953450348</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.126008581423943</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.10150927869516645</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>9.3098781159968086E-2</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.11315047894239405</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.12235330257627881</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.66633267926556194</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.70909055913759678</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.72409740805667899</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.80532553270103069</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.74143477427960047</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.75789020257670014</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.89434582259369833</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.81843563980173684</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.77082440062094348</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>0.8324393941822229</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>0.7228790498576847</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.7557268340491488</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.7557268340491488</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.6988232968892629</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.6214187737279036</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.6830670581808651</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.6585493875400987</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.4798117897994847</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.5265836333092251</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.4924472496531587</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.3921048654750781</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.5627496988409393</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>0.15648173464349882</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>0.15054731209829122</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>0.13982521087583435</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.19137515367616401</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.18891807492705495</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.19872992719638863</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.16676775724774287</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.12682675384151482</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>0.10710221167462976</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>0.13112363264516025</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.13821995863778755</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.3242609217741999</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.2501559971022376</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.1502475870069577</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.5107145414111571</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.3991769532085905</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.2733437042835725</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.8837317773933846</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.56592689857679968</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.46947505670260209</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.55616759512623426</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.58288029845511569</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.5946807003557232E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>1.3242609217741999</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>1.2501559971022376</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.1502475870069577</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.5107145414111571</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.3991769532085905</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.2733437042835725</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.8837317773933846</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.56592689857679968</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.46947505670260209</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.55616759512623426</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.58288029845511569</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>5.5946807003557232E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>5.2816053954467153E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>4.8595166328980047E-2</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>6.3824019493500514E-2</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>5.9111827342990725E-2</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>5.3795678254481297E-2</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>3.733552080242436E-2</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>2.3909036695259806E-2</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>1.983418068029582E-2</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>2.3496729832118049E-2</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>2.4625276656320898E-2</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>7.100027059867195E-2</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>6.7078531597119101E-2</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.1716720527540171E-2</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>7.7647958870631972E-2</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>6.723521326031863E-2</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.0400678627456355E-2</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.6878698116494114E-2</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.6866381282256466E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.9985636402381988E-2</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.0496587669786111E-2</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15442,6 +15464,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15463,13 +15486,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15486,20 +15509,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15510,7 +15533,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15520,7 +15543,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15529,9 +15552,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15541,15 +15564,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15559,13 +15582,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15575,13 +15598,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15591,13 +15614,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15611,7 +15634,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15642,7 +15665,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15652,13 +15675,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15666,9 +15689,9 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15676,7 +15699,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15701,7 +15724,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16473,7 +16496,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16510,7 +16533,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16731,7 +16754,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16960,19 +16983,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17097,7 +17120,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17223,18 +17246,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17246,31 +17269,31 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
-        <v>536206397.52000004</v>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
+        <v>482585757.76800007</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17280,7 +17303,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17289,29 +17312,29 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>8936773292.0000019</v>
+        <v>8043095962.8000011</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.666666666666671</v>
+        <v>15.900000000000002</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17324,7 +17347,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17334,13 +17357,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1">
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17348,9 +17371,9 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1">
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17358,13 +17381,13 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>19.187148831068647</v>
+        <v>17.268433947961782</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17380,16 +17403,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17399,7 +17422,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>566348617.92693233</v>
+        <v>509713756.1342392</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17411,7 +17434,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>534291148.98767197</v>
+        <v>480862034.08890486</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17421,7 +17444,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>598185248.27612245</v>
+        <v>538366723.44851029</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17433,7 +17456,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>532382741.43478316</v>
+        <v>479144467.29130495</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17443,7 +17466,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>631811537.85623121</v>
+        <v>568630384.07060814</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17455,7 +17478,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>530481150.42638475</v>
+        <v>477433035.38374633</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17465,7 +17488,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>667328090.28415155</v>
+        <v>600595281.25573647</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17477,7 +17500,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>528586351.61480606</v>
+        <v>475727716.45332551</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17487,7 +17510,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>704841164.49235678</v>
+        <v>634357048.04312122</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17499,7 +17522,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>526698320.73934239</v>
+        <v>474028488.66540825</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18055,11 +18078,11 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>9439143632.1155396</v>
+        <v>8495229268.9039869</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18071,7 +18094,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>7053477223.9549341</v>
+        <v>6348129501.5594416</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18082,7 +18105,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>9705916937.1579227</v>
+        <v>8735325243.442131</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18092,7 +18115,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18103,7 +18126,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>9705916937.1579227</v>
+        <v>8735325243.442131</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18133,19 +18156,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>8936773291.9999981</v>
+        <v>8043095962.7999983</v>
       </c>
       <c r="C51" s="123">
-        <v>9204002730.5397282</v>
+        <v>8283602457.485754</v>
       </c>
       <c r="D51" s="123">
-        <v>9478239572.3840122</v>
+        <v>8530415615.1456127</v>
       </c>
       <c r="E51" s="123">
-        <v>9759793481.9879837</v>
+        <v>8783814133.7891846</v>
       </c>
       <c r="F51" s="123">
-        <v>10048983755.62377</v>
+        <v>9044085380.0613937</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18154,19 +18177,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>8936773291.9999981</v>
+        <v>8043095962.7999973</v>
       </c>
       <c r="C52" s="123">
-        <v>9456197261.4376793</v>
+        <v>8510577535.2939081</v>
       </c>
       <c r="D52" s="123">
-        <v>10025819700.569693</v>
+        <v>9023237730.5127239</v>
       </c>
       <c r="E52" s="123">
-        <v>10651726355.650965</v>
+        <v>9586553720.0858688</v>
       </c>
       <c r="F52" s="123">
-        <v>11340689093.753593</v>
+        <v>10206620184.378235</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18175,19 +18198,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>8936773291.9999962</v>
+        <v>8043095962.7999954</v>
       </c>
       <c r="C53" s="123">
-        <v>9798162917.5209427</v>
+        <v>8818346625.7688465</v>
       </c>
       <c r="D53" s="123">
-        <v>10807836591.388325</v>
+        <v>9727052932.2494926</v>
       </c>
       <c r="E53" s="123">
-        <v>11995839408.294106</v>
+        <v>10796255467.464691</v>
       </c>
       <c r="F53" s="123">
-        <v>13398231803.134014</v>
+        <v>12058408622.820614</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18196,19 +18219,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>8936773291.9999962</v>
+        <v>8043095962.7999954</v>
       </c>
       <c r="C54" s="123">
-        <v>10180351442.878204</v>
+        <v>9162316298.5903816</v>
       </c>
       <c r="D54" s="123">
-        <v>11731167802.123228</v>
+        <v>10558051021.910906</v>
       </c>
       <c r="E54" s="123">
-        <v>13677847795.288212</v>
+        <v>12310063015.759386</v>
       </c>
       <c r="F54" s="123">
-        <v>16135063076.593027</v>
+        <v>14521556768.933723</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18217,19 +18240,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>8936773291.9999943</v>
+        <v>8043095962.7999954</v>
       </c>
       <c r="C55" s="123">
-        <v>10570436985.22624</v>
+        <v>9513393286.7036152</v>
       </c>
       <c r="D55" s="123">
-        <v>12729303828.752592</v>
+        <v>11456373445.877329</v>
       </c>
       <c r="E55" s="123">
-        <v>15612351232.449381</v>
+        <v>14051116109.204435</v>
       </c>
       <c r="F55" s="123">
-        <v>19496992135.855938</v>
+        <v>17547292922.270344</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18238,19 +18261,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>8936773291.9999943</v>
+        <v>8043095962.7999945</v>
       </c>
       <c r="C56" s="123">
-        <v>10948141020.922453</v>
+        <v>9853326918.8302059</v>
       </c>
       <c r="D56" s="123">
-        <v>13755342369.301622</v>
+        <v>12379808132.371458</v>
       </c>
       <c r="E56" s="123">
-        <v>17735533659.456116</v>
+        <v>15961980293.510492</v>
       </c>
       <c r="F56" s="123">
-        <v>23455035048.056538</v>
+        <v>21109531543.250881</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18263,7 +18286,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18300,23 +18323,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>17.666666666666671</v>
+        <v>15.900000000000002</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>17.666666666666671</v>
+        <v>15.900000000000002</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>17.666666666666671</v>
+        <v>15.900000000000002</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>17.666666666666671</v>
+        <v>15.900000000000002</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>17.666666666666671</v>
+        <v>15.900000000000002</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18327,23 +18350,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.666666666666664</v>
+        <v>15.899999999999997</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>18.194939373151012</v>
+        <v>16.375445435835911</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>18.737064669864019</v>
+        <v>16.86335820287762</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>19.29365471720503</v>
+        <v>17.364289245484525</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>19.865340716237704</v>
+        <v>17.878806644613935</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18354,23 +18377,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666664</v>
+        <v>15.899999999999995</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>18.693490311722865</v>
+        <v>16.824141280550574</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>19.819548837455791</v>
+        <v>17.837593953710215</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>21.056872855697112</v>
+        <v>18.9511855701274</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>22.418849336706081</v>
+        <v>20.176964403035473</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18381,23 +18404,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666661</v>
+        <v>15.899999999999991</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>19.36950536324925</v>
+        <v>17.432554826924321</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>21.365479486738714</v>
+        <v>19.228931538064842</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>23.713983704040892</v>
+        <v>21.342585333636794</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>26.486304111640759</v>
+        <v>23.837673700476685</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18408,23 +18431,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666661</v>
+        <v>15.899999999999991</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>20.125035022634911</v>
+        <v>18.112531520371416</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>23.190767450302207</v>
+        <v>20.871690705271988</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>27.039063185486746</v>
+        <v>24.335156866938064</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>31.896610969753819</v>
+        <v>28.706949872778434</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18435,23 +18458,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666654</v>
+        <v>15.899999999999991</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>20.896175905700364</v>
+        <v>18.806558315130324</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>25.16393336760677</v>
+        <v>22.647540030846084</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>30.863287687236291</v>
+        <v>27.776958918512648</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>38.542642832299371</v>
+        <v>34.688378549069434</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18461,40 +18484,40 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666654</v>
+        <v>15.89999999999999</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>21.642840398495885</v>
+        <v>19.478556358646294</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>27.19225838948681</v>
+        <v>24.473032550538125</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>35.060502384853159</v>
+        <v>31.554452146367822</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>46.3671027908849</v>
+        <v>41.730392511796403</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18512,7 +18535,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>22.418849336706081</v>
+        <v>20.176964403035473</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18534,7 +18557,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>19.29365471720503</v>
+        <v>17.364289245484525</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18557,7 +18580,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>18.737064669864019</v>
+        <v>16.86335820287762</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18580,7 +18603,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>18.194939373151012</v>
+        <v>16.375445435835911</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18603,7 +18626,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>17.666666666666664</v>
+        <v>15.899999999999995</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18619,7 +18642,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18671,32 +18694,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="6" width="42.6640625" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="6" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18708,14 +18731,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18723,7 +18746,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.06</v>
+        <v>0.95400000000000007</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18732,7 +18755,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.06</v>
+        <v>0.95400000000000007</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18744,7 +18767,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18752,12 +18775,12 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>28.806753827145844</v>
+        <v>28.700753827145846</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18767,11 +18790,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洽洽食品(002557.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18792,8 +18815,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18814,8 +18837,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18825,8 +18848,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18837,10 +18860,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>447</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>444</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18851,15 +18874,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>6.0153753070249838E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18870,14 +18893,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9591718766888921E-2</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18894,12 +18917,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.6842771130545571E-2</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18908,38 +18931,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18949,12 +18972,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18964,44 +18987,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19011,55 +19034,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19069,55 +19092,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19127,24 +19150,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19157,7 +19180,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19166,12 +19189,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19186,39 +19209,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19228,55 +19251,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.1</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19286,23 +19309,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.15</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19313,7 +19336,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19322,7 +19345,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19331,15 +19354,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19347,19 +19370,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>5.62138395706255E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19375,20 +19398,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19398,19 +19421,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19420,14 +19443,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19436,7 +19459,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19445,12 +19468,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19460,11 +19483,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
-        <v>1.06</v>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
+        <v>0.95400000000000007</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19473,25 +19496,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.829322250329541</v>
+        <v>1.6463900252965866</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19499,7 +19522,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19513,18 +19536,18 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>13.438941031541804</v>
+        <v>13.256008806508849</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.51565717866448546</v>
+        <v>0.5222501021528535</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19532,12 +19555,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19550,11 +19573,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.6969308965579426E-2</v>
+        <v>9.2706938820872553E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19562,12 +19585,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19576,11 +19599,11 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.279132885208865</v>
+        <v>2.0512195966879787</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19588,7 +19611,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19602,30 +19625,30 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>18.869653870203344</v>
+        <v>18.641740581682459</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.31993291944146818</v>
+        <v>0.32814697179298713</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19636,11 +19659,11 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.8333926664293383</v>
+        <v>2.5500533997864046</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19648,7 +19671,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19660,21 +19683,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>26.130102221251306</v>
+        <v>25.846762954608369</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>5.8264531266100761E-2</v>
+        <v>6.8476149836260602E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19682,12 +19705,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19696,17 +19719,17 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.6975834619563113</v>
+        <v>2.4278251157606801</v>
       </c>
       <c r="D103" s="116"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19716,21 +19739,21 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>24.301055185803946</v>
+        <v>24.031296839608316</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.12428977531548846</v>
+        <v>0.13401075821731312</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19738,32 +19761,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>325</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F11C926-F602-4890-8B9F-41C5C2211925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A882224-1277-4B0B-B39E-C6166F6BB49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.67</v>
+        <v>23.71</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11973.590027640001</v>
+        <v>11993.824231319999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.2706938820872553E-2</v>
+        <v>9.2069270412264093E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.5946807003557232E-2</v>
+        <v>5.5852421837798392E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.0304182509505702E-2</v>
+        <v>4.0236187262758329E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.6463900252965866</v>
+        <v>1.6463900252965868</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.0304182509505702E-2</v>
+        <v>4.0236187262758329E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.0304182509505702E-2</v>
+        <v>4.0236187262758329E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.5946807003557232E-2</v>
+        <v>5.5852421837798392E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.2816053954467153E-2</v>
+        <v>5.2726950531515715E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.8595166328980047E-2</v>
+        <v>4.8513183762419136E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.3824019493500514E-2</v>
+        <v>6.3716345061626198E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.9111827342990725E-2</v>
+        <v>5.9012102623727983E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.3795678254481297E-2</v>
+        <v>5.3704922154515916E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.733552080242436E-2</v>
+        <v>3.7272533841981634E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.3909036695259806E-2</v>
+        <v>2.386870091002951E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.983418068029582E-2</v>
+        <v>1.9800719388553441E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.3496729832118049E-2</v>
+        <v>2.345708962995505E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.4625276656320898E-2</v>
+        <v>2.4583732537120019E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.100027059867195E-2</v>
+        <v>7.0880489458901949E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7078531597119101E-2</v>
+        <v>6.6965366634492166E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1716720527540171E-2</v>
+        <v>8.1578860180804555E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7647958870631972E-2</v>
+        <v>7.7516962735886083E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.723521326031863E-2</v>
+        <v>6.7121783967597742E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0400678627456355E-2</v>
+        <v>5.0315650067983643E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6878698116494114E-2</v>
+        <v>3.6816481839621079E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6866381282256466E-2</v>
+        <v>2.6821056303290198E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9985636402381988E-2</v>
+        <v>2.9935049078210957E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0496587669786111E-2</v>
+        <v>3.0445138344320426E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.67</v>
+        <v>-23.71</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.67</v>
+        <v>23.71</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6463900252965866</v>
+        <v>1.6463900252965868</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.67</v>
+        <v>23.71</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.2706938820872553E-2</v>
+        <v>9.2069270412264093E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A882224-1277-4B0B-B39E-C6166F6BB49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822B026F-8D2E-4CD4-9B3E-85EE3A3A2569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.71</v>
+        <v>23.06</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11993.824231319999</v>
+        <v>11665.018421519999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.2069270412264093E-2</v>
+        <v>0.10261755079069901</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.5852421837798392E-2</v>
+        <v>5.7426752895672159E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.0236187262758329E-2</v>
+        <v>4.1370338248048574E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.0236187262758329E-2</v>
+        <v>4.1370338248048574E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.0236187262758329E-2</v>
+        <v>4.1370338248048574E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.5852421837798392E-2</v>
+        <v>5.7426752895672159E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.2726950531515715E-2</v>
+        <v>5.4213182875205448E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.8513183762419136E-2</v>
+        <v>4.9880641240544574E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.3716345061626198E-2</v>
+        <v>6.551233917654628E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.9012102623727983E-2</v>
+        <v>6.0675496669930204E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.3704922154515916E-2</v>
+        <v>5.521872091429196E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.7272533841981634E-2</v>
+        <v>3.8323147328420841E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.386870091002951E-2</v>
+        <v>2.4541496035420628E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.9800719388553441E-2</v>
+        <v>2.0358848946340075E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.345708962995505E-2</v>
+        <v>2.4118282529324991E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.4583732537120019E-2</v>
+        <v>2.5276682500221845E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0880489458901949E-2</v>
+        <v>7.2878421728992421E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6965366634492166E-2</v>
+        <v>6.885294201664395E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1578860180804555E-2</v>
+        <v>8.3878351035857598E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7516962735886083E-2</v>
+        <v>7.9701959517253215E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7121783967597742E-2</v>
+        <v>6.9013768337889955E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0315650067983643E-2</v>
+        <v>5.173391427198145E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6816481839621079E-2</v>
+        <v>3.7854240434406584E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6821056303290198E-2</v>
+        <v>2.7577070466219024E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9935049078210957E-2</v>
+        <v>3.077883840608768E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0445138344320426E-2</v>
+        <v>3.1303305730435271E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.71</v>
+        <v>-23.06</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.71</v>
+        <v>23.06</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.71</v>
+        <v>23.06</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.2069270412264093E-2</v>
+        <v>0.10261755079069901</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822B026F-8D2E-4CD4-9B3E-85EE3A3A2569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86032DAE-F08D-4585-89B3-E64F0D6C0826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.06</v>
+        <v>22.95</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11665.018421519999</v>
+        <v>11609.3743614</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10261755079069901</v>
+        <v>0.10444287078173975</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.7426752895672159E-2</v>
+        <v>5.7702000948766874E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.1370338248048574E-2</v>
+        <v>4.1568627450980396E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.1370338248048574E-2</v>
+        <v>4.1568627450980396E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.1370338248048574E-2</v>
+        <v>4.1568627450980396E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7426752895672159E-2</v>
+        <v>5.7702000948766874E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.4213182875205448E-2</v>
+        <v>5.4473028196175929E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.9880641240544574E-2</v>
+        <v>5.0119720566751971E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.551233917654628E-2</v>
+        <v>6.5826341673688768E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.0675496669930204E-2</v>
+        <v>6.0966316043947297E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.521872091429196E-2</v>
+        <v>5.5483385807563075E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.8323147328420841E-2</v>
+        <v>3.850683125897101E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.4541496035420628E-2</v>
+        <v>2.4659124120993452E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.0358848946340075E-2</v>
+        <v>2.0456429485952162E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.4118282529324991E-2</v>
+        <v>2.4233882140576656E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.5276682500221845E-2</v>
+        <v>2.5397834355342732E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2878421728992421E-2</v>
+        <v>7.3227730068434208E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.885294201664395E-2</v>
+        <v>6.9182956117813041E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3878351035857598E-2</v>
+        <v>8.4280382348012037E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9701959517253215E-2</v>
+        <v>8.0083973266573377E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9013768337889955E-2</v>
+        <v>6.9344553284171773E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.173391427198145E-2</v>
+        <v>5.1981876388317742E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7854240434406584E-2</v>
+        <v>3.803567688093315E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7577070466219024E-2</v>
+        <v>2.7709248146013533E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.077883840608768E-2</v>
+        <v>3.092636225029986E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1303305730435271E-2</v>
+        <v>3.1453343361387248E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.06</v>
+        <v>-22.95</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.06</v>
+        <v>22.95</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.06</v>
+        <v>22.95</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10261755079069901</v>
+        <v>0.10444287078173975</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86032DAE-F08D-4585-89B3-E64F0D6C0826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353ACA51-6602-4ECB-B5B5-802AA5344C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.95</v>
+        <v>21.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11609.3743614</v>
+        <v>10875.884478</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10444287078173975</v>
+        <v>0.1296800450140696</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.7702000948766874E-2</v>
+        <v>6.1593531245311618E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.1568627450980396E-2</v>
+        <v>4.4372093023255815E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.1568627450980396E-2</v>
+        <v>4.4372093023255815E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.1568627450980396E-2</v>
+        <v>4.4372093023255815E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7702000948766874E-2</v>
+        <v>6.1593531245311618E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.4473028196175929E-2</v>
+        <v>5.8146790562894769E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.0119720566751971E-2</v>
+        <v>5.3499887767765479E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.5826341673688768E-2</v>
+        <v>7.0265792623774748E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.0966316043947297E-2</v>
+        <v>6.5077997823655365E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.5483385807563075E-2</v>
+        <v>5.922528857132895E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.850683125897101E-2</v>
+        <v>4.1103803599692304E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.4659124120993452E-2</v>
+        <v>2.6322181329153472E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.0456429485952162E-2</v>
+        <v>2.1836049148958238E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.4233882140576656E-2</v>
+        <v>2.5868260238429499E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.5397834355342732E-2</v>
+        <v>2.7110711556051891E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3227730068434208E-2</v>
+        <v>7.8166344421886746E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9182956117813041E-2</v>
+        <v>7.3848783390874848E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4280382348012037E-2</v>
+        <v>8.996440813427331E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0083973266573377E-2</v>
+        <v>8.5484985417109721E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9344553284171773E-2</v>
+        <v>7.4021278970778717E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1981876388317742E-2</v>
+        <v>5.5487630842413586E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.803567688093315E-2</v>
+        <v>4.0600873693833292E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7709248146013533E-2</v>
+        <v>2.9578011393070262E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.092636225029986E-2</v>
+        <v>3.3012093657878223E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1453343361387248E-2</v>
+        <v>3.3574615355527318E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.95</v>
+        <v>-21.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.95</v>
+        <v>21.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.95</v>
+        <v>21.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10444287078173975</v>
+        <v>0.1296800450140696</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353ACA51-6602-4ECB-B5B5-802AA5344C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46222C09-3591-49B7-A0B5-618000A77F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.5</v>
+        <v>21.39</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10875.884478</v>
+        <v>10820.240417880001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1296800450140696</v>
+        <v>0.1316893009668183</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1593531245311618E-2</v>
+        <v>6.1910281522870481E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4372093023255815E-2</v>
+        <v>4.4600280504908836E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4372093023255815E-2</v>
+        <v>4.4600280504908836E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4372093023255815E-2</v>
+        <v>4.4600280504908836E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1593531245311618E-2</v>
+        <v>6.1910281522870481E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8146790562894769E-2</v>
+        <v>5.8445815666303767E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3499887767765479E-2</v>
+        <v>5.3775015755350992E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>7.0265792623774748E-2</v>
+        <v>7.0627140785935349E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.5077997823655365E-2</v>
+        <v>6.5412667284179077E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.922528857132895E-2</v>
+        <v>5.9529859947806095E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.1103803599692304E-2</v>
+        <v>4.1315183608853882E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6322181329153472E-2</v>
+        <v>2.6457545515511906E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1836049148958238E-2</v>
+        <v>2.1948342996849092E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5868260238429499E-2</v>
+        <v>2.6001290094728107E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.7110711556051891E-2</v>
+        <v>2.7250130830066183E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8166344421886746E-2</v>
+        <v>7.8568321882681855E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3848783390874848E-2</v>
+        <v>7.422855740550767E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.996440813427331E-2</v>
+        <v>9.0427058199479937E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5484985417109721E-2</v>
+        <v>8.5924599647866237E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4021278970778717E-2</v>
+        <v>7.4401940059454982E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5487630842413586E-2</v>
+        <v>5.577298097764806E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0600873693833292E-2</v>
+        <v>4.0809667340692642E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9578011393070262E-2</v>
+        <v>2.9730118978541865E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3012093657878223E-2</v>
+        <v>3.3181861320447953E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3574615355527318E-2</v>
+        <v>3.374727583655153E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.5</v>
+        <v>-21.39</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.5</v>
+        <v>21.39</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.5</v>
+        <v>21.39</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1296800450140696</v>
+        <v>0.1316893009668183</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46222C09-3591-49B7-A0B5-618000A77F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878CD5DF-6A49-4480-BD46-0BCC4C67DF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.39</v>
+        <v>21.61</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10820.240417880001</v>
+        <v>10931.528538119999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1316893009668183</v>
+        <v>0.12768480202511756</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1910281522870481E-2</v>
+        <v>6.1280005635085608E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4600280504908836E-2</v>
+        <v>4.4146228597871359E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4600280504908836E-2</v>
+        <v>4.4146228597871359E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4600280504908836E-2</v>
+        <v>4.4146228597871359E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1910281522870481E-2</v>
+        <v>6.1280005635085608E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8445815666303767E-2</v>
+        <v>5.7850809676179435E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3775015755350992E-2</v>
+        <v>5.3227560712955008E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>7.0627140785935349E-2</v>
+        <v>6.9908123156462623E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.5412667284179077E-2</v>
+        <v>6.4746735456205018E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.9529859947806095E-2</v>
+        <v>5.8923817875223161E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.1315183608853882E-2</v>
+        <v>4.0894575538796142E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6457545515511906E-2</v>
+        <v>2.6188195214104568E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1948342996849092E-2</v>
+        <v>2.1724898505442021E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.6001290094728107E-2</v>
+        <v>2.5736584688858595E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.7250130830066183E-2</v>
+        <v>2.6972711636053481E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8568321882681855E-2</v>
+        <v>7.7768459281377392E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.422855740550767E-2</v>
+        <v>7.3472875654965727E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0427058199479937E-2</v>
+        <v>8.9506468065103026E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5924599647866237E-2</v>
+        <v>8.5049846666721857E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4401940059454982E-2</v>
+        <v>7.3644493191658611E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.577298097764806E-2</v>
+        <v>5.5205185706242124E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0809667340692642E-2</v>
+        <v>4.0394205664850337E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9730118978541865E-2</v>
+        <v>2.9427452334614097E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3181861320447953E-2</v>
+        <v>3.2844054310244418E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.374727583655153E-2</v>
+        <v>3.3403712639696319E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.39</v>
+        <v>-21.61</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.39</v>
+        <v>21.61</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.39</v>
+        <v>21.61</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1316893009668183</v>
+        <v>0.12768480202511756</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878CD5DF-6A49-4480-BD46-0BCC4C67DF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFCFD7A-0481-4458-A300-8E0A4217CE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.61</v>
+        <v>21.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10931.528538119999</v>
+        <v>10977.0554964</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12768480202511756</v>
+        <v>0.12606263492724823</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1280005635085608E-2</v>
+        <v>6.1025848929686627E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4146228597871359E-2</v>
+        <v>4.3963133640553001E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4146228597871359E-2</v>
+        <v>4.3963133640553001E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4146228597871359E-2</v>
+        <v>4.3963133640553001E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1280005635085608E-2</v>
+        <v>6.1025848929686627E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7850809676179435E-2</v>
+        <v>5.7610875442499432E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3227560712955008E-2</v>
+        <v>5.3006801244560267E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.9908123156462623E-2</v>
+        <v>6.9618181631850559E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.4746735456205018E-2</v>
+        <v>6.4478200608690805E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.8923817875223161E-2</v>
+        <v>5.8679433377123155E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.0894575538796142E-2</v>
+        <v>4.0724966700155976E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6188195214104568E-2</v>
+        <v>2.6079580579576024E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1724898505442021E-2</v>
+        <v>2.1634795239751248E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5736584688858595E-2</v>
+        <v>2.5629843093374852E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.6972711636053481E-2</v>
+        <v>2.6860843246779526E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7768459281377392E-2</v>
+        <v>7.7445917284357846E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3472875654965727E-2</v>
+        <v>7.3168149442571856E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9506468065103026E-2</v>
+        <v>8.9135243082344523E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5049846666721857E-2</v>
+        <v>8.4697105367182446E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3644493191658611E-2</v>
+        <v>7.3339055201462777E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5205185706242124E-2</v>
+        <v>5.497622410653881E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0394205664850337E-2</v>
+        <v>4.0226672092968471E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9427452334614097E-2</v>
+        <v>2.9305402993134128E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2844054310244418E-2</v>
+        <v>3.2707834730155844E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3403712639696319E-2</v>
+        <v>3.3265171896029372E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.61</v>
+        <v>-21.7</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.61</v>
+        <v>21.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.61</v>
+        <v>21.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12768480202511756</v>
+        <v>0.12606263492724823</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFCFD7A-0481-4458-A300-8E0A4217CE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5DBC84-165C-457C-A1AB-BE44F9C39290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.7</v>
+        <v>21.51</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10977.0554964</v>
+        <v>10880.943028920001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12606263492724823</v>
+        <v>0.12949808280561848</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1025848929686627E-2</v>
+        <v>6.1564896409772189E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.3963133640553001E-2</v>
+        <v>4.4351464435146447E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.3963133640553001E-2</v>
+        <v>4.4351464435146447E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.3963133640553001E-2</v>
+        <v>4.4351464435146447E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1025848929686627E-2</v>
+        <v>6.1564896409772189E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7610875442499432E-2</v>
+        <v>5.8119758117258835E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3006801244560267E-2</v>
+        <v>5.3475015667455029E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.9618181631850559E-2</v>
+        <v>7.0233126053517295E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.4478200608690805E-2</v>
+        <v>6.5047743059441679E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.8679433377123155E-2</v>
+        <v>5.9197754731918753E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.0724966700155976E-2</v>
+        <v>4.1084694439487889E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6079580579576024E-2</v>
+        <v>2.6309944145829829E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1634795239751248E-2</v>
+        <v>2.1825897568693728E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5629843093374852E-2</v>
+        <v>2.5856234083042037E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.6860843246779526E-2</v>
+        <v>2.7098107784989105E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7445917284357846E-2</v>
+        <v>7.8130004884731055E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3168149442571856E-2</v>
+        <v>7.3814451088043201E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9135243082344523E-2</v>
+        <v>8.992258367674924E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4697105367182446E-2</v>
+        <v>8.5445243443415114E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3339055201462777E-2</v>
+        <v>7.3986866474743951E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.497622410653881E-2</v>
+        <v>5.5461834640255329E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0226672092968471E-2</v>
+        <v>4.0581998345765494E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9305402993134128E-2</v>
+        <v>2.9564260574198541E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2707834730155844E-2</v>
+        <v>3.2996746334001945E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3265171896029372E-2</v>
+        <v>3.3559006515287648E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.7</v>
+        <v>-21.51</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.7</v>
+        <v>21.51</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.7</v>
+        <v>21.51</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12606263492724823</v>
+        <v>0.12949808280561848</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5DBC84-165C-457C-A1AB-BE44F9C39290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D456702-5BE0-46C0-A625-E3004947488A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.51</v>
+        <v>21.55</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10880.943028920001</v>
+        <v>10901.177232600001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12949808280561848</v>
+        <v>0.12877138948591438</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1564896409772189E-2</v>
+        <v>6.145062282014848E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4351464435146447E-2</v>
+        <v>4.4269141531322505E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4351464435146447E-2</v>
+        <v>4.4269141531322505E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4351464435146447E-2</v>
+        <v>4.4269141531322505E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1564896409772189E-2</v>
+        <v>6.145062282014848E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8119758117258835E-2</v>
+        <v>5.8011879215881093E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3475015667455029E-2</v>
+        <v>5.3375758097770662E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>7.0233126053517295E-2</v>
+        <v>7.0102762942513094E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.5047743059441679E-2</v>
+        <v>6.4927004789261736E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.9197754731918753E-2</v>
+        <v>5.9087874908750462E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.1084694439487889E-2</v>
+        <v>4.1008435145864712E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6309944145829829E-2</v>
+        <v>2.6261108982682118E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1825897568693728E-2</v>
+        <v>2.1785385461837684E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5856234083042037E-2</v>
+        <v>2.5808241073143119E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.7098107784989105E-2</v>
+        <v>2.7047809673091214E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8130004884731055E-2</v>
+        <v>7.7984983993993742E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3814451088043201E-2</v>
+        <v>7.3677440505977229E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.992258367674924E-2</v>
+        <v>8.9755674008671738E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5445243443415114E-2</v>
+        <v>8.5286644383659349E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3986866474743951E-2</v>
+        <v>7.3849535864117966E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5461834640255329E-2</v>
+        <v>5.5358889239530952E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0581998345765494E-2</v>
+        <v>4.0506672130738546E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9564260574198541E-2</v>
+        <v>2.9509384916520214E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2996746334001945E-2</v>
+        <v>3.2935499473057156E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3559006515287648E-2</v>
+        <v>3.349671601595533E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.51</v>
+        <v>-21.55</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.51</v>
+        <v>21.55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.51</v>
+        <v>21.55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12949808280561848</v>
+        <v>0.12877138948591438</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D456702-5BE0-46C0-A625-E3004947488A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BD36A5-67B7-4B6B-8AE3-34385271F9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.55</v>
+        <v>21.46</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10901.177232600001</v>
+        <v>10855.65027432</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12877138948591438</v>
+        <v>0.13040905320925367</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>13.256008806508849</v>
+        <v>12.895318326330678</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>18.641740581682459</v>
+        <v>16.068545959498671</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4544,7 +4544,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.145062282014848E-2</v>
+        <v>6.1708337454529347E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4269141531322505E-2</v>
+        <v>4.4454799627213423E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.6463900252965868</v>
+        <v>1.6178692272519435</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.609618781212262</v>
+        <v>11.277449099078733</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>13.256008806508849</v>
+        <v>12.895318326330678</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5222501021528535</v>
+        <v>0.53524947795101596</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.0512195966879787</v>
+        <v>1.8622080000000001</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>16.59052098499448</v>
+        <v>14.206337959498672</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>18.641740581682459</v>
+        <v>16.068545959498671</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.32814697179298713</v>
+        <v>0.42088555441112108</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4269141531322505E-2</v>
+        <v>4.4454799627213423E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4269141531322505E-2</v>
+        <v>4.4454799627213423E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.145062282014848E-2</v>
+        <v>6.1708337454529347E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8011879215881093E-2</v>
+        <v>5.8255172278762236E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3375758097770662E-2</v>
+        <v>5.3599607968637358E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>7.0102762942513094E-2</v>
+        <v>7.0396763346279451E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.4927004789261736E-2</v>
+        <v>6.5199298844761902E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.9087874908750462E-2</v>
+        <v>5.9335680535115211E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.1008435145864712E-2</v>
+        <v>4.1180418331471791E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6261108982682118E-2</v>
+        <v>2.6371244108890943E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1785385461837684E-2</v>
+        <v>2.1876750079338401E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5808241073143119E-2</v>
+        <v>2.5916476939712687E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.7047809673091214E-2</v>
+        <v>2.7161244103220673E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7984983993993742E-2</v>
+        <v>7.8312041242803596E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3677440505977229E-2</v>
+        <v>7.3986432567745078E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9755674008671738E-2</v>
+        <v>9.0132095754281272E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5286644383659349E-2</v>
+        <v>8.5644323693749261E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3849535864117966E-2</v>
+        <v>7.4159249667835145E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5358889239530952E-2</v>
+        <v>5.5591056062995907E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0506672130738546E-2</v>
+        <v>4.0676550998015648E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9509384916520214E-2</v>
+        <v>2.9633142821575517E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2935499473057156E-2</v>
+        <v>3.3073625985292725E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.349671601595533E-2</v>
+        <v>3.3637196185640136E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.55</v>
+        <v>-21.46</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.55</v>
+        <v>21.46</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6463900252965868</v>
+        <v>1.6178692272519435</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.609618781212262</v>
+        <v>11.277449099078733</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>13.256008806508849</v>
+        <v>12.895318326330678</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.5222501021528535</v>
+        <v>0.53524947795101596</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.55</v>
+        <v>21.46</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12877138948591438</v>
+        <v>0.13040905320925367</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.0512195966879787</v>
+        <v>1.8622080000000001</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>16.59052098499448</v>
+        <v>14.206337959498672</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>18.641740581682459</v>
+        <v>16.068545959498671</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.32814697179298713</v>
+        <v>0.42088555441112108</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BD36A5-67B7-4B6B-8AE3-34385271F9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B0ACB9-9476-4037-BBB8-CD8D2D158B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.46</v>
+        <v>21.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10855.65027432</v>
+        <v>10875.884478</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13040905320925367</v>
+        <v>0.1296800450140696</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1708337454529347E-2</v>
+        <v>6.1593531245311618E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4454799627213423E-2</v>
+        <v>4.4372093023255815E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4454799627213423E-2</v>
+        <v>4.4372093023255815E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4454799627213423E-2</v>
+        <v>4.4372093023255815E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1708337454529347E-2</v>
+        <v>6.1593531245311618E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8255172278762236E-2</v>
+        <v>5.8146790562894769E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3599607968637358E-2</v>
+        <v>5.3499887767765479E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>7.0396763346279451E-2</v>
+        <v>7.0265792623774748E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.5199298844761902E-2</v>
+        <v>6.5077997823655365E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.9335680535115211E-2</v>
+        <v>5.922528857132895E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.1180418331471791E-2</v>
+        <v>4.1103803599692304E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6371244108890943E-2</v>
+        <v>2.6322181329153472E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1876750079338401E-2</v>
+        <v>2.1836049148958238E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5916476939712687E-2</v>
+        <v>2.5868260238429499E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.7161244103220673E-2</v>
+        <v>2.7110711556051891E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8312041242803596E-2</v>
+        <v>7.8166344421886746E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3986432567745078E-2</v>
+        <v>7.3848783390874848E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0132095754281272E-2</v>
+        <v>8.996440813427331E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5644323693749261E-2</v>
+        <v>8.5484985417109721E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4159249667835145E-2</v>
+        <v>7.4021278970778717E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5591056062995907E-2</v>
+        <v>5.5487630842413586E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0676550998015648E-2</v>
+        <v>4.0600873693833292E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9633142821575517E-2</v>
+        <v>2.9578011393070262E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3073625985292725E-2</v>
+        <v>3.3012093657878223E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3637196185640136E-2</v>
+        <v>3.3574615355527318E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.46</v>
+        <v>-21.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.46</v>
+        <v>21.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.46</v>
+        <v>21.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13040905320925367</v>
+        <v>0.1296800450140696</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B0ACB9-9476-4037-BBB8-CD8D2D158B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B78A02-64C4-48C3-9261-980624AB5C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10875.884478</v>
+        <v>10977.0554964</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1296800450140696</v>
+        <v>0.12606263492724823</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1593531245311618E-2</v>
+        <v>6.1025848929686627E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4372093023255815E-2</v>
+        <v>4.3963133640553001E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4372093023255815E-2</v>
+        <v>4.3963133640553001E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4372093023255815E-2</v>
+        <v>4.3963133640553001E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1593531245311618E-2</v>
+        <v>6.1025848929686627E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8146790562894769E-2</v>
+        <v>5.7610875442499432E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3499887767765479E-2</v>
+        <v>5.3006801244560267E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>7.0265792623774748E-2</v>
+        <v>6.9618181631850559E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.5077997823655365E-2</v>
+        <v>6.4478200608690805E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.922528857132895E-2</v>
+        <v>5.8679433377123155E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.1103803599692304E-2</v>
+        <v>4.0724966700155976E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6322181329153472E-2</v>
+        <v>2.6079580579576024E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1836049148958238E-2</v>
+        <v>2.1634795239751248E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5868260238429499E-2</v>
+        <v>2.5629843093374852E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.7110711556051891E-2</v>
+        <v>2.6860843246779526E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8166344421886746E-2</v>
+        <v>7.7445917284357846E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3848783390874848E-2</v>
+        <v>7.3168149442571856E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.996440813427331E-2</v>
+        <v>8.9135243082344523E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5484985417109721E-2</v>
+        <v>8.4697105367182446E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4021278970778717E-2</v>
+        <v>7.3339055201462777E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5487630842413586E-2</v>
+        <v>5.497622410653881E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0600873693833292E-2</v>
+        <v>4.0226672092968471E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9578011393070262E-2</v>
+        <v>2.9305402993134128E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3012093657878223E-2</v>
+        <v>3.2707834730155844E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3574615355527318E-2</v>
+        <v>3.3265171896029372E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.5</v>
+        <v>-21.7</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1296800450140696</v>
+        <v>0.12606263492724823</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B78A02-64C4-48C3-9261-980624AB5C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED40CB6-D37F-4753-AA7B-6A989FF045EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>CN</t>
@@ -4240,13 +4244,13 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4277,7 +4281,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4324,10 +4328,10 @@
         <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4421,7 +4425,7 @@
         <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4429,7 +4433,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4442,7 +4446,7 @@
         <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4450,7 +4454,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -6610,7 +6614,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12780,7 +12784,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19803,4 +19807,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED40CB6-D37F-4753-AA7B-6A989FF045EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D44087-EC43-462D-8521-F10CF193F31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2504,7 +2517,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2944,6 +2957,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3147,11 +3166,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3936,9 +3956,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{6F32F958-783B-416E-82AA-E97A42DE9DC2}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4023,6 +4049,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>505855092</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>21.7</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19810,22 +19919,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6639A61D-07BC-4CF4-8D56-E4716B6AC59B}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D44087-EC43-462D-8521-F10CF193F31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BE2DD4-8BE2-4EF3-895B-F6DC21FED2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3920,47 +3920,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4449,7 +4449,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.7</v>
+        <v>21.83</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10977.0554964</v>
+        <v>11042.81665836</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4507,13 +4507,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4589,14 +4589,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>27.746753827145845</v>
+        <v>23.068262059109994</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12606263492724823</v>
+        <v>6.1492528673418922E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>12.895318326330678</v>
+        <v>8.9913803957882639</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4638,7 +4638,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>16.068545959498671</v>
+        <v>12.232463386030947</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4657,7 +4657,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>25.846762954608369</v>
+        <v>21.049942920535798</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4676,7 +4676,7 @@
         <v>433</v>
       </c>
       <c r="F31" s="312">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>24.031296839608316</v>
+        <v>20.388648577016472</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4713,13 +4713,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4740,13 +4740,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4766,13 +4766,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4801,13 +4801,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4893,13 +4893,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4915,13 +4915,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4937,22 +4937,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1025848929686627E-2</v>
+        <v>6.0662433429876317E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.3963133640553001E-2</v>
+        <v>4.3701328447091167E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -5087,13 +5087,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5146,22 +5146,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.071015362903331</v>
+        <v>17.656812290322666</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5198,13 +5198,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5217,13 +5217,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5345,13 +5345,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>25.850567581066237</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5390,13 +5390,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>31.79 CNY</v>
+        <v>26.62 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>27.88 CNY</v>
+        <v>23.17 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>27.19 CNY</v>
+        <v>22.57 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>26.51 CNY</v>
+        <v>22 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>25.85 CNY</v>
+        <v>21.44 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>27.746753827145845</v>
+        <v>23.068262059109994</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5539,13 +5539,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5558,22 +5558,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.6178692272519435</v>
+        <v>1.4246045348312761</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.277449099078733</v>
+        <v>7.5667758609569873</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>12.895318326330678</v>
+        <v>8.9913803957882639</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53524947795101596</v>
+        <v>0.61022723026343306</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>1.8622080000000001</v>
+        <v>1.7325716886663638</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>14.206337959498672</v>
+        <v>10.499891697364584</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>16.068545959498671</v>
+        <v>12.232463386030947</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.42088555441112108</v>
+        <v>0.46972756965017359</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.5500533997864046</v>
+        <v>2.4809015558378498</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>23.296709554821966</v>
+        <v>18.569041364697949</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>25.846762954608369</v>
+        <v>21.049942920535798</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>6.8476149836260602E-2</v>
+        <v>8.7493333195299505E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>21.603471723847637</v>
+        <v>17.960823461255792</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>24.031296839608316</v>
+        <v>20.388648577016472</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.13401075821731312</v>
+        <v>0.11554003116982536</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5906,13 +5906,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5920,13 +5920,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5949,13 +5949,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5963,22 +5963,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6002,6 +6002,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6018,17 +6029,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.3963133640553001E-2</v>
+        <v>4.3701328447091167E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.3963133640553001E-2</v>
+        <v>4.3701328447091167E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14796,50 +14796,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1025848929686627E-2</v>
+        <v>6.0662433429876317E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7610875442499432E-2</v>
+        <v>5.7267796477427288E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3006801244560267E-2</v>
+        <v>5.2691140036965546E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.9618181631850559E-2</v>
+        <v>6.9203597865834049E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.4478200608690805E-2</v>
+        <v>6.409422598298628E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.8679433377123155E-2</v>
+        <v>5.8329991034520044E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.0724966700155976E-2</v>
+        <v>4.0482445139412945E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6079580579576024E-2</v>
+        <v>2.5924273869757201E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1634795239751248E-2</v>
+        <v>2.1505957705112329E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5629843093374852E-2</v>
+        <v>2.547721461870061E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.6860843246779526E-2</v>
+        <v>2.6700884033674564E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14853,43 +14853,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7445917284357846E-2</v>
+        <v>7.6984718509874733E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3168149442571856E-2</v>
+        <v>7.2732425236088388E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9135243082344523E-2</v>
+        <v>8.8604433114378212E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4697105367182446E-2</v>
+        <v>8.4192724987075557E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3339055201462777E-2</v>
+        <v>7.2902313232787105E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.497622410653881E-2</v>
+        <v>5.4648834773792593E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0226672092968471E-2</v>
+        <v>3.9987117930252669E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9305402993134128E-2</v>
+        <v>2.9130886163582715E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2707834730155844E-2</v>
+        <v>3.251305605333861E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3265171896029372E-2</v>
+        <v>3.3067074216392003E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15671,16 +15671,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11164735506.934877</v>
+        <v>8931788405.5479031</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15695,8 +15695,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15711,8 +15711,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15727,8 +15727,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>13076641241.972479</v>
+        <v>10843694140.585506</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15765,7 +15765,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>25.850567581066237</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>27.750110140096613</v>
+        <v>23.052087483375182</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15861,11 +15861,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>667491405.14548194</v>
+        <v>658177571.58531249</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15883,11 +15883,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>665107226.32934093</v>
+        <v>646675590.70083082</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15905,11 +15905,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>662731563.44102097</v>
+        <v>635374612.6611414</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15937,11 +15937,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>660364386.06290972</v>
+        <v>624271124.84141672</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15969,11 +15969,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>658005663.88604224</v>
+        <v>613361676.00169873</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>11792348157.570181</v>
+        <v>9433878526.0561447</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16621,11 +16621,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>8811928538.0263062</v>
+        <v>6571249523.8667984</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16636,7 +16636,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>12125628782.891102</v>
+        <v>9749110099.6571999</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16657,7 +16657,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>12125628782.891102</v>
+        <v>9749110099.6571999</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16687,19 +16687,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>11164735506.934874</v>
+        <v>8931788405.5479031</v>
       </c>
       <c r="C56" s="123">
-        <v>11498585981.091312</v>
+        <v>9215019911.3940392</v>
       </c>
       <c r="D56" s="123">
-        <v>11841190823.511272</v>
+        <v>9506502503.7688847</v>
       </c>
       <c r="E56" s="123">
-        <v>12192936898.852106</v>
+        <v>9806598901.0010681</v>
       </c>
       <c r="F56" s="123">
-        <v>12554223104.826691</v>
+        <v>10115683064.939873</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16708,19 +16708,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>11164735506.934872</v>
+        <v>8931788405.547905</v>
       </c>
       <c r="C57" s="123">
-        <v>11813653303.688793</v>
+        <v>9495880292.9507923</v>
       </c>
       <c r="D57" s="123">
-        <v>12525284186.998447</v>
+        <v>10116150416.270252</v>
       </c>
       <c r="E57" s="123">
-        <v>13307231096.434795</v>
+        <v>10799344001.136341</v>
       </c>
       <c r="F57" s="123">
-        <v>14167954144.19693</v>
+        <v>11552962013.623589</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16729,19 +16729,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>11164735506.934868</v>
+        <v>8931788405.547905</v>
       </c>
       <c r="C58" s="341">
-        <v>12240871940.424587</v>
+        <v>9851482426.5496807</v>
       </c>
       <c r="D58" s="123">
-        <v>13502260044.24229</v>
+        <v>10929105214.295393</v>
       </c>
       <c r="E58" s="123">
-        <v>14986435238.002663</v>
+        <v>12196189597.198746</v>
       </c>
       <c r="F58" s="123">
-        <v>16738447922.417589</v>
+        <v>13690522494.195721</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16760,19 +16760,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>11164735506.934868</v>
+        <v>8931788405.547905</v>
       </c>
       <c r="C59" s="341">
-        <v>12718341118.614334</v>
+        <v>10222203452.311735</v>
       </c>
       <c r="D59" s="123">
-        <v>14655780270.875019</v>
+        <v>11824447920.723272</v>
       </c>
       <c r="E59" s="123">
-        <v>17087772952.146759</v>
+        <v>13826659352.519575</v>
       </c>
       <c r="F59" s="123">
-        <v>20157578776.126354</v>
+        <v>16342545283.065136</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16791,19 +16791,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>11164735506.934868</v>
+        <v>8931788405.5479069</v>
       </c>
       <c r="C60" s="341">
-        <v>13205676061.897917</v>
+        <v>10575044307.034138</v>
       </c>
       <c r="D60" s="123">
-        <v>15902754360.195995</v>
+        <v>12726985307.00481</v>
       </c>
       <c r="E60" s="123">
-        <v>19504553428.43959</v>
+        <v>15575253377.481741</v>
       </c>
       <c r="F60" s="123">
-        <v>24357646016.653687</v>
+        <v>19380222546.216766</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16822,19 +16822,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>11164735506.934868</v>
+        <v>8931788405.5479069</v>
       </c>
       <c r="C61" s="341">
-        <v>13677542754.793108</v>
+        <v>10893580614.04991</v>
       </c>
       <c r="D61" s="123">
-        <v>17184587137.067047</v>
+        <v>13591996865.061111</v>
       </c>
       <c r="E61" s="123">
-        <v>22157051086.819511</v>
+        <v>17364545809.187386</v>
       </c>
       <c r="F61" s="123">
-        <v>29302439936.778774</v>
+        <v>22714472922.908939</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16914,23 +16914,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>25.850567581066237</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>25.850567581066237</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>25.850567581066237</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>25.850567581066237</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>25.850567581066237</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16941,23 +16941,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>25.85056758106623</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>26.510540129403136</v>
+        <v>21.996270913156373</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>27.187818756895851</v>
+        <v>22.57248848412598</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>27.88316823721863</v>
+        <v>23.165734261381459</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>28.597377131600158</v>
+        <v>23.776747511671729</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16968,23 +16968,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>25.85056758106623</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>27.133381191162144</v>
+        <v>22.551489959081792</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>28.540169211217609</v>
+        <v>23.777671395483065</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>30.085961517754967</v>
+        <v>25.128243121794931</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>31.787482489618853</v>
+        <v>26.618033428160473</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16995,23 +16995,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>25.850567581066223</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>27.977928658395694</v>
+        <v>23.254462290926753</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>30.471504632555707</v>
+        <v>25.384761668729023</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>33.405497424626631</v>
+        <v>27.889598336268897</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>36.86896495143948</v>
+        <v>30.843671391239695</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17022,23 +17022,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>25.850567581066223</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>28.921813944401173</v>
+        <v>23.987322415545318</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>32.751841916642448</v>
+        <v>27.154720537558362</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>37.559528386015266</v>
+        <v>31.112793636872546</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>43.628076222199923</v>
+        <v>36.086324536005137</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17049,23 +17049,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>25.850567581066223</v>
+        <v>21.436364508485585</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>29.885202375180437</v>
+        <v>24.684836111270656</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>35.216923535947323</v>
+        <v>28.93890221439624</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>42.33714259710802</v>
+        <v>34.569502984303931</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>51.93098214713887</v>
+        <v>42.091359003764602</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17075,23 +17075,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>25.850567581066223</v>
+        <v>21.436364508485585</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>30.818012384128991</v>
+        <v>25.314534837355183</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>37.750915576638405</v>
+        <v>30.648900930898833</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>47.580734488004552</v>
+        <v>38.106667006180878</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>61.706101540668833</v>
+        <v>48.682674242896702</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.787482489618853</v>
+        <v>26.618033428160473</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17148,7 +17148,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>27.88316823721863</v>
+        <v>23.165734261381459</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>27.187818756895851</v>
+        <v>22.57248848412598</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>26.510540129403136</v>
+        <v>21.996270913156373</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>25.85056758106623</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17431,14 +17431,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>8043095962.8000011</v>
+        <v>6434476770.2400007</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>15.900000000000002</v>
+        <v>12.72</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>17.268433947961782</v>
+        <v>13.883969798323109</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17543,11 +17543,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>480862034.08890486</v>
+        <v>474152331.28766435</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17565,11 +17565,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>479144467.29130495</v>
+        <v>465866283.13554168</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17587,11 +17587,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>477433035.38374633</v>
+        <v>457725037.80194104</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17609,11 +17609,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>475727716.45332551</v>
+        <v>449726064.78548634</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17631,11 +17631,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>474028488.66540825</v>
+        <v>441866877.80657345</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>8495229268.9039869</v>
+        <v>6796183415.1231899</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18203,11 +18203,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>6348129501.5594416</v>
+        <v>4733940224.8387508</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>8735325243.442131</v>
+        <v>7023276819.6559582</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18239,7 +18239,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>8735325243.442131</v>
+        <v>7023276819.6559582</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18269,19 +18269,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>8043095962.7999983</v>
+        <v>6434476770.2400017</v>
       </c>
       <c r="C51" s="123">
-        <v>8283602457.485754</v>
+        <v>6638517267.1952419</v>
       </c>
       <c r="D51" s="123">
-        <v>8530415615.1456127</v>
+        <v>6848501862.0385695</v>
       </c>
       <c r="E51" s="123">
-        <v>8783814133.7891846</v>
+        <v>7064691857.7200365</v>
       </c>
       <c r="F51" s="123">
-        <v>9044085380.0613937</v>
+        <v>7287356657.0426416</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18290,19 +18290,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>8043095962.7999973</v>
+        <v>6434476770.2400026</v>
       </c>
       <c r="C52" s="123">
-        <v>8510577535.2939081</v>
+        <v>6840849601.857934</v>
       </c>
       <c r="D52" s="123">
-        <v>9023237730.5127239</v>
+        <v>7287693337.7993193</v>
       </c>
       <c r="E52" s="123">
-        <v>9586553720.0858688</v>
+        <v>7779867250.9953947</v>
       </c>
       <c r="F52" s="123">
-        <v>10206620184.378235</v>
+        <v>8322775051.1814842</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18311,19 +18311,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>8043095962.7999954</v>
+        <v>6434476770.2400017</v>
       </c>
       <c r="C53" s="123">
-        <v>8818346625.7688465</v>
+        <v>7097026031.9521122</v>
       </c>
       <c r="D53" s="123">
-        <v>9727052932.2494926</v>
+        <v>7873347467.2566156</v>
       </c>
       <c r="E53" s="123">
-        <v>10796255467.464691</v>
+        <v>8786157383.6515598</v>
       </c>
       <c r="F53" s="123">
-        <v>12058408622.820614</v>
+        <v>9862677546.9326401</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18332,19 +18332,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>8043095962.7999954</v>
+        <v>6434476770.2400017</v>
       </c>
       <c r="C54" s="123">
-        <v>9162316298.5903816</v>
+        <v>7364094139.7258949</v>
       </c>
       <c r="D54" s="123">
-        <v>10558051021.910906</v>
+        <v>8518353997.2294436</v>
       </c>
       <c r="E54" s="123">
-        <v>12310063015.759386</v>
+        <v>9960750789.6792107</v>
       </c>
       <c r="F54" s="123">
-        <v>14521556768.933723</v>
+        <v>11773199634.371248</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18353,19 +18353,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>8043095962.7999954</v>
+        <v>6434476770.2400026</v>
       </c>
       <c r="C55" s="123">
-        <v>9513393286.7036152</v>
+        <v>7618281339.4464712</v>
       </c>
       <c r="D55" s="123">
-        <v>11456373445.877329</v>
+        <v>9168543587.781599</v>
       </c>
       <c r="E55" s="123">
-        <v>14051116109.204435</v>
+        <v>11220441136.487123</v>
       </c>
       <c r="F55" s="123">
-        <v>17547292922.270344</v>
+        <v>13961547913.322262</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18374,19 +18374,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>8043095962.7999945</v>
+        <v>6434476770.2400026</v>
       </c>
       <c r="C56" s="123">
-        <v>9853326918.8302059</v>
+        <v>7847755480.0002165</v>
       </c>
       <c r="D56" s="123">
-        <v>12379808132.371458</v>
+        <v>9791699502.7655621</v>
       </c>
       <c r="E56" s="123">
-        <v>15961980293.510492</v>
+        <v>12509450690.254082</v>
       </c>
       <c r="F56" s="123">
-        <v>21109531543.250881</v>
+        <v>16363548007.912916</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18436,23 +18436,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>15.900000000000002</v>
+        <v>12.72</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>15.900000000000002</v>
+        <v>12.72</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>15.900000000000002</v>
+        <v>12.72</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>15.900000000000002</v>
+        <v>12.72</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>15.900000000000002</v>
+        <v>12.72</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18463,23 +18463,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>15.899999999999997</v>
+        <v>12.720000000000004</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>16.375445435835911</v>
+        <v>13.123357602171259</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>16.86335820287762</v>
+        <v>13.538465798499008</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>17.364289245484525</v>
+        <v>13.965841145906735</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>17.878806644613935</v>
+        <v>14.406016213518004</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18490,23 +18490,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>15.899999999999995</v>
+        <v>12.720000000000006</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>16.824141280550574</v>
+        <v>13.523338422494191</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>17.837593953710215</v>
+        <v>14.406681781112365</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>18.9511855701274</v>
+        <v>15.379636133020076</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>20.176964403035473</v>
+        <v>16.452883805667977</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18517,23 +18517,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>15.899999999999991</v>
+        <v>12.720000000000004</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>17.432554826924321</v>
+        <v>14.02976098133675</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>19.228931538064842</v>
+        <v>15.564432565317768</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>21.342585333636794</v>
+        <v>17.368921500648963</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>23.837673700476685</v>
+        <v>19.497041154490624</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18544,23 +18544,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>15.899999999999991</v>
+        <v>12.720000000000004</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>18.112531520371416</v>
+        <v>14.557714760981185</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>20.871690705271988</v>
+        <v>16.839514184883292</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>24.335156866938064</v>
+        <v>19.690917314477108</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>28.706949872778434</v>
+        <v>23.273858107908989</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18571,23 +18571,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>15.899999999999991</v>
+        <v>12.720000000000006</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>18.806558315130324</v>
+        <v>15.060204908338594</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>22.647540030846084</v>
+        <v>18.124841941457809</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>27.776958918512648</v>
+        <v>22.181137076479452</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>34.688378549069434</v>
+        <v>27.599895966495996</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18597,23 +18597,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>15.89999999999999</v>
+        <v>12.720000000000006</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>19.478556358646294</v>
+        <v>15.513841027027196</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>24.473032550538125</v>
+        <v>19.35672815717265</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>31.554452146367822</v>
+        <v>24.729316533704246</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>41.730392511796403</v>
+        <v>32.348291569461786</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>20.176964403035473</v>
+        <v>16.452883805667977</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18670,7 +18670,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>17.364289245484525</v>
+        <v>13.965841145906735</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>16.86335820287762</v>
+        <v>13.538465798499008</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18716,7 +18716,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>16.375445435835911</v>
+        <v>13.123357602171259</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>15.899999999999995</v>
+        <v>12.720000000000006</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.7</v>
+        <v>-21.83</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>28.700753827145846</v>
+        <v>24.022262059109995</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18903,11 +18903,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洽洽食品(002557.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18928,8 +18928,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18950,8 +18950,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18961,8 +18961,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18975,8 +18975,8 @@
       <c r="B11" s="159" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18994,8 +18994,8 @@
         <v>6.0153753070249838E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19012,8 +19012,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9591718766888921E-2</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19030,8 +19030,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.6842771130545571E-2</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19057,21 +19057,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19079,14 +19079,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.7</v>
+        <v>21.83</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19094,14 +19094,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>25.850567581066237</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19121,8 +19121,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19132,8 +19132,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19141,14 +19141,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>27.187818756895851</v>
+        <v>22.57248848412598</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19158,8 +19158,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19179,8 +19179,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19190,8 +19190,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19199,14 +19199,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>26.510540129403136</v>
+        <v>21.996270913156373</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19216,8 +19216,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19237,8 +19237,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19248,8 +19248,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19257,14 +19257,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>27.88316823721863</v>
+        <v>23.165734261381459</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19275,8 +19275,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>27.191432927461861</v>
+        <v>22.575894125383151</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19338,8 +19338,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19349,8 +19349,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19358,14 +19358,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>25.85056758106623</v>
+        <v>21.436364508485578</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19375,8 +19375,8 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19396,8 +19396,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19407,8 +19407,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19416,14 +19416,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>31.787482489618853</v>
+        <v>26.618033428160473</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19433,8 +19433,8 @@
         <v>0.15</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>27.746753827145845</v>
+        <v>23.068262059109994</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>27.750110140096613</v>
+        <v>23.052087483375182</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.13621601437445302</v>
+        <v>0.16384208782084247</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6178692272519435</v>
+        <v>1.4246045348312761</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.277449099078733</v>
+        <v>7.5667758609569873</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>12.895318326330678</v>
+        <v>8.9913803957882639</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19660,7 +19660,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53524947795101596</v>
+        <v>0.61022723026343306</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.7</v>
+        <v>21.83</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12606263492724823</v>
+        <v>6.1492528673418922E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.8622080000000001</v>
+        <v>1.7325716886663638</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19728,7 +19728,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>14.206337959498672</v>
+        <v>10.499891697364584</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>16.068545959498671</v>
+        <v>12.232463386030947</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.42088555441112108</v>
+        <v>0.46972756965017359</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.5500533997864046</v>
+        <v>2.4809015558378498</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>23.296709554821966</v>
+        <v>18.569041364697949</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>25.846762954608369</v>
+        <v>21.049942920535798</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>6.8476149836260602E-2</v>
+        <v>8.7493333195299505E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>21.603471723847637</v>
+        <v>17.960823461255792</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>24.031296839608316</v>
+        <v>20.388648577016472</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.13401075821731312</v>
+        <v>0.11554003116982536</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19923,19 +19923,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BE2DD4-8BE2-4EF3-895B-F6DC21FED2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D896F325-3174-415A-BD41-339BEE2C9D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="561">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2334,133 +2126,1148 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>CN</t>
@@ -3171,7 +3978,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3920,33 +4727,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3961,10 +4790,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{6F32F958-783B-416E-82AA-E97A42DE9DC2}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{1B8D6C5A-0416-4123-AC4D-75349063DA20}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4076,7 +4910,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>21.7</v>
+            <v>21.83</v>
           </cell>
         </row>
         <row r="13">
@@ -4101,7 +4935,7 @@
         </row>
         <row r="86">
           <cell r="C86">
-            <v>0.06</v>
+            <v>7.4999999999999997E-2</v>
           </cell>
         </row>
         <row r="92">
@@ -4331,6 +5165,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45797</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>CN</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>洽洽食品</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>505855092</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>002557.SZ</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>21.83</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>11042.81665836</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>CNS_01</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (CNY) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>23.068262059109994</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>6.1492528673418922E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>002557.SZ (CNY)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>8.9913803957882639</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>12.232463386030947</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>21.049942920535798</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>20.388648577016472</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>923979255.39561176</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>32042840.928504106</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-59672121</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>-27629280.071495894</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-2378351.0769942678</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-224087493.83102897</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>632397776.92850411</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>669884130.41609263</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>6.0662433429876317E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>4.3701328447091167E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>0.80044648495694337</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>0.15648173464349882</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.15054731209829122</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>0.13375671427886937</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.12092451547494525</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.66633267926556194</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.70909055913759678</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.7557268340491488</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.7557268340491488</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>17.656812290322666</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>2209595736.0500002</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>4.3680409093321932</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>0.3857437197038544</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>2.3913910654887354</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>4583178463.29</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>3530916331.352602</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>6.9800944720995357</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>590585139.73500001</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.1674986553955653</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>21.436364508485578</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>3.5427832354191278</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.08</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>26.62 CNY</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.06</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>23.17 CNY</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.04</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>22.57 CNY</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.44999999999999996</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.02</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>22 CNY</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>21.44 CNY</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>23.068262059109994</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.95400000000000007</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>002557.SZ</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>1.4246045348312761</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>7.5667758609569873</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>8.9913803957882639</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.61022723026343306</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>1.7325716886663638</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>10.499891697364584</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>12.232463386030947</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.46972756965017359</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>2.4809015558378498</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>18.569041364697949</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>21.049942920535798</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>8.7493333195299505E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>2.4278251157606801</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>17.960823461255792</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>20.388648577016472</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.11554003116982536</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4347,24 +6924,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4378,7 +6955,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4387,15 +6964,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>505855092</v>
@@ -4404,7 +6981,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4414,7 +6991,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4427,26 +7004,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>21.83</v>
@@ -4456,17 +7033,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4480,7 +7057,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4494,7 +7071,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4507,71 +7084,71 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="361" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
-      <c r="F18" s="361"/>
+      <c r="B18" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
         <v/>
       </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4592,7 +7169,7 @@
         <v>23.068262059109994</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4605,7 +7182,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4616,7 +7193,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4624,7 +7201,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4635,7 +7212,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F29" s="302">
         <v>0.45</v>
@@ -4643,7 +7220,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4654,7 +7231,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F30" s="312">
         <v>0.3</v>
@@ -4662,7 +7239,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4673,7 +7250,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4681,7 +7258,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4692,7 +7269,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4704,7 +7281,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4712,27 +7289,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="361" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4740,17 +7317,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="362" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4766,17 +7343,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="362" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="362"/>
-      <c r="D43" s="362"/>
-      <c r="E43" s="362"/>
-      <c r="F43" s="362"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4789,7 +7366,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4801,17 +7378,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="362"/>
-      <c r="D47" s="362"/>
-      <c r="E47" s="362"/>
-      <c r="F47" s="362"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4823,17 +7400,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="362" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="362"/>
-      <c r="D50" s="362"/>
-      <c r="E50" s="362"/>
-      <c r="F50" s="362"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4848,7 +7425,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4863,7 +7440,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4876,12 +7453,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4893,17 +7470,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="362"/>
-      <c r="D58" s="362"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="362"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4915,17 +7492,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="362" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="365"/>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="B61" s="367" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4937,26 +7514,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="361" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="361"/>
-      <c r="D64" s="361"/>
-      <c r="E64" s="361"/>
-      <c r="F64" s="361"/>
+      <c r="B64" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="361" t="s">
-        <v>358</v>
-      </c>
-      <c r="C65" s="361"/>
-      <c r="D65" s="361"/>
-      <c r="E65" s="361"/>
-      <c r="F65" s="361"/>
+      <c r="B65" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4969,7 +7546,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4982,7 +7559,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4992,14 +7569,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>4.3701328447091167E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -5008,18 +7585,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -5074,7 +7651,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5085,33 +7662,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="361" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="361"/>
-      <c r="D80" s="361"/>
-      <c r="E80" s="361"/>
-      <c r="F80" s="361"/>
+      <c r="B80" s="371" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5120,7 +7697,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5129,7 +7706,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5141,31 +7718,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="361" t="s">
-        <v>360</v>
-      </c>
-      <c r="C89" s="361"/>
-      <c r="D89" s="361"/>
-      <c r="E89" s="361"/>
-      <c r="F89" s="361"/>
+      <c r="B89" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="361" t="s">
-        <v>361</v>
-      </c>
-      <c r="C90" s="361"/>
-      <c r="D90" s="361"/>
-      <c r="E90" s="361"/>
-      <c r="F90" s="361"/>
+      <c r="B90" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5173,7 +7750,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5186,7 +7763,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5198,36 +7775,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="361" t="s">
-        <v>362</v>
-      </c>
-      <c r="C97" s="361"/>
-      <c r="D97" s="361"/>
-      <c r="E97" s="361"/>
-      <c r="F97" s="361"/>
+      <c r="B97" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="361" t="s">
-        <v>341</v>
-      </c>
-      <c r="C101" s="361"/>
-      <c r="D101" s="361"/>
-      <c r="E101" s="361"/>
-      <c r="F101" s="361"/>
+      <c r="B101" s="371" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5240,7 +7817,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5253,7 +7830,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5262,7 +7839,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5271,12 +7848,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5289,7 +7866,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5302,7 +7879,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5315,12 +7892,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5333,7 +7910,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5345,17 +7922,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="361" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="361"/>
-      <c r="D116" s="361"/>
-      <c r="E116" s="361"/>
-      <c r="F116" s="361"/>
+      <c r="B116" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5368,7 +7945,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5381,7 +7958,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5389,30 +7966,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="362" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>473</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5527,7 +8104,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5539,17 +8116,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="366" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="366"/>
-      <c r="D134" s="366"/>
-      <c r="E134" s="366"/>
-      <c r="F134" s="366"/>
+      <c r="B134" s="369" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5558,31 +8135,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="364" t="s">
-        <v>365</v>
-      </c>
-      <c r="C138" s="364"/>
-      <c r="D138" s="364"/>
-      <c r="E138" s="364"/>
-      <c r="F138" s="364"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="361" t="s">
-        <v>366</v>
-      </c>
-      <c r="C139" s="361"/>
-      <c r="D139" s="361"/>
-      <c r="E139" s="361"/>
-      <c r="F139" s="361"/>
+      <c r="B138" s="370" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5591,7 +8168,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5600,7 +8177,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5613,7 +8190,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5626,7 +8203,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5655,7 +8232,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5668,7 +8245,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5681,7 +8258,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5690,12 +8267,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5724,7 +8301,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5737,7 +8314,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5750,7 +8327,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5759,12 +8336,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5793,7 +8370,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5806,7 +8383,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5819,7 +8396,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5828,12 +8405,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5862,7 +8439,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5875,7 +8452,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5888,7 +8465,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5897,7 +8474,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5906,113 +8483,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="368" t="s">
-        <v>373</v>
-      </c>
-      <c r="C179" s="361"/>
-      <c r="D179" s="361"/>
-      <c r="E179" s="361"/>
-      <c r="F179" s="361"/>
+      <c r="B179" s="372" t="s">
+        <v>477</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="365" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="365"/>
-      <c r="D182" s="365"/>
-      <c r="E182" s="365"/>
-      <c r="F182" s="365"/>
+      <c r="B182" s="373" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="362" t="s">
-        <v>378</v>
-      </c>
-      <c r="C188" s="362"/>
-      <c r="D188" s="362"/>
-      <c r="E188" s="362"/>
-      <c r="F188" s="362"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>478</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="367" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" s="367"/>
-      <c r="D191" s="367"/>
-      <c r="E191" s="367"/>
-      <c r="F191" s="367"/>
+      <c r="B191" s="368" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="367" t="s">
-        <v>380</v>
-      </c>
-      <c r="C192" s="367"/>
-      <c r="D192" s="367"/>
-      <c r="E192" s="367"/>
-      <c r="F192" s="367"/>
+      <c r="B192" s="368" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6029,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6053,7 +8630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6118,7 +8695,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6134,7 +8711,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1</v>
@@ -6142,7 +8719,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>7131364079</v>
@@ -6178,7 +8755,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>5145338820</v>
@@ -6214,7 +8791,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>1020355341</v>
@@ -6250,7 +8827,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>712355118</v>
@@ -6286,7 +8863,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351">
         <v>75683892</v>
@@ -6322,7 +8899,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6338,7 +8915,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6354,7 +8931,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6370,7 +8947,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>59672121</v>
@@ -6400,7 +8977,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>139564139</v>
@@ -6430,7 +9007,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>229311604</v>
@@ -6466,7 +9043,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>850128132</v>
@@ -6502,7 +9079,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>647365</v>
@@ -6538,13 +9115,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351"/>
       <c r="D19" s="351"/>
@@ -6560,7 +9137,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6576,7 +9153,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6592,7 +9169,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>1038904494</v>
@@ -6628,7 +9205,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>-581740675</v>
@@ -6664,7 +9241,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-435769097</v>
@@ -6720,15 +9297,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6765,7 +9342,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6802,7 +9379,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6839,7 +9416,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6876,7 +9453,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6913,7 +9490,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6929,12 +9506,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -6983,7 +9560,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7032,7 +9609,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -7081,7 +9658,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7130,7 +9707,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7179,7 +9756,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7228,7 +9805,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7277,7 +9854,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7326,7 +9903,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7375,7 +9952,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7424,7 +10001,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7473,7 +10050,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7522,7 +10099,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7571,12 +10148,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7625,7 +10202,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7674,12 +10251,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7728,7 +10305,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7777,7 +10354,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7826,7 +10403,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7875,13 +10452,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7930,7 +10507,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -7979,7 +10556,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -8028,7 +10605,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8077,7 +10654,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -8126,7 +10703,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8181,7 +10758,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8280,7 +10857,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8379,7 +10956,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -8395,13 +10972,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8450,7 +11027,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8484,7 +11061,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8518,7 +11095,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8567,7 +11144,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8639,7 +11216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8659,7 +11236,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8675,7 +11252,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8686,27 +11263,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <f>64090000+418378550.52+6446920.18</f>
@@ -8717,7 +11294,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <v>4583178463.29</v>
@@ -8728,7 +11305,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -8738,7 +11315,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -8749,7 +11326,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>1545872989.1700001</v>
@@ -8759,7 +11336,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8770,7 +11347,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8780,7 +11357,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>304944913.81999999</v>
@@ -8791,7 +11368,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8801,7 +11378,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8812,7 +11389,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <v>63782145.289999999</v>
@@ -8822,7 +11399,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8833,7 +11410,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>0</v>
@@ -8845,7 +11422,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <v>406953110.22000003</v>
@@ -8857,7 +11434,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8868,7 +11445,7 @@
         <v>1093011647.0449998</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8886,27 +11463,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8915,7 +11492,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8926,7 +11503,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>218481267.78999999</v>
@@ -8935,7 +11512,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8946,7 +11523,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8955,7 +11532,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <v>664145486.29999995</v>
@@ -8966,7 +11543,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8975,7 +11552,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8986,7 +11563,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <f>1326974361.16+5553565.01</f>
@@ -8996,7 +11573,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>91308996.629999995</v>
@@ -9007,7 +11584,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -9016,7 +11593,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -9027,7 +11604,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>285880529</v>
@@ -9036,7 +11613,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9047,7 +11624,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>64397018.740000002</v>
@@ -9059,7 +11636,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <f>1931.1+6666621.46</f>
@@ -9072,7 +11649,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -9083,7 +11660,7 @@
         <v>314744769.82800001</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -9096,30 +11673,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>850003104.54999995</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -9132,13 +11709,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>2154785.64</v>
@@ -9147,13 +11724,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9166,13 +11743,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -9182,14 +11759,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>850003104.54999995</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -9199,14 +11776,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>2033032766.8</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -9219,7 +11796,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>2883035871.3499999</v>
@@ -9232,24 +11809,24 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H34" s="198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F35" s="199" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
@@ -9262,13 +11839,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19">
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9278,13 +11855,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19">
         <v>2885347.22</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9294,13 +11871,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9310,13 +11887,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19">
         <v>1356707284.28</v>
       </c>
       <c r="F39" s="190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
@@ -9329,14 +11906,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>1359592631.5</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9349,14 +11926,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>86283945.589999914</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9369,13 +11946,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="84">
         <v>1445876577.0899999</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9388,7 +11965,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -9399,21 +11976,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="F45" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9445,20 +12022,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D49" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -9472,7 +12049,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9486,19 +12063,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="253"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9512,7 +12089,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9529,19 +12106,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C57" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" s="253"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -9552,7 +12129,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -9566,19 +12143,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="253"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9589,12 +12166,12 @@
         <v>3.7631672027541312E-4</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9605,21 +12182,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F65" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9630,12 +12207,12 @@
         <v>3530916331.352602</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9645,7 +12222,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9655,7 +12232,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9665,7 +12242,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9678,19 +12255,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C72" s="234" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D72" s="182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F72" s="253"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9701,12 +12278,12 @@
         <v>-526131065.96869904</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9717,12 +12294,12 @@
         <v>8.7110964543626963</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9730,12 +12307,12 @@
         <v>1052262131.9373981</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9743,7 +12320,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9751,19 +12328,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D78" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" s="253"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9777,7 +12354,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9791,7 +12368,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9805,7 +12382,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9819,7 +12396,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9830,15 +12407,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9855,7 +12432,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9872,7 +12449,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9889,7 +12466,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9911,7 +12488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9937,7 +12514,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9990,12 +12567,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -10013,7 +12590,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -10027,7 +12604,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="327">
         <f>AVERAGE(G4:J4)</f>
@@ -10084,7 +12661,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="328">
         <f>C25</f>
@@ -10139,7 +12716,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
@@ -10194,7 +12771,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="328">
         <f>C35</f>
@@ -10249,7 +12826,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10306,7 +12883,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="328">
         <f>BS!$G$39*BS!D58</f>
@@ -10361,7 +12938,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
@@ -10416,7 +12993,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10473,7 +13050,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="328">
         <f>C50</f>
@@ -10528,7 +13105,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10583,7 +13160,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -10638,7 +13215,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10695,7 +13272,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10752,7 +13329,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="328">
         <f>-C4*C85</f>
@@ -10760,7 +13337,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10778,14 +13355,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="328">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10803,7 +13380,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
@@ -10879,12 +13456,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10902,7 +13479,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10923,7 +13500,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
@@ -10980,7 +13557,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
@@ -11037,7 +13614,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
@@ -11098,14 +13675,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
@@ -11113,7 +13690,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11173,7 +13750,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11224,7 +13801,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -11283,21 +13860,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-301299427</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11347,7 +13924,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="340">
         <f>AVERAGE(G34:J34)</f>
@@ -11355,7 +13932,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11406,7 +13983,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
@@ -11467,7 +14044,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11590,7 +14167,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -11649,21 +14226,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11717,12 +14294,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11740,14 +14317,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -11802,7 +14379,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11857,7 +14434,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11914,7 +14491,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
@@ -11973,24 +14550,24 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="87">
         <f>G53</f>
         <v>3.0451386547102714E-2</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -12010,14 +14587,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>2.7005899779057908E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12037,7 +14614,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -12096,17 +14673,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12161,7 +14738,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12216,7 +14793,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12271,7 +14848,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12326,13 +14903,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12382,7 +14959,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12441,17 +15018,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12476,7 +15053,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12501,7 +15078,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12526,7 +15103,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12556,12 +15133,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12579,7 +15156,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12600,7 +15177,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -12657,7 +15234,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12714,7 +15291,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12771,7 +15348,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12828,7 +15405,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12885,7 +15462,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12893,7 +15470,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12944,7 +15521,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -13001,7 +15578,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -13058,7 +15635,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13115,7 +15692,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -13230,7 +15807,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13287,7 +15864,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C85" s="264">
         <v>0</v>
@@ -13313,7 +15890,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -13337,7 +15914,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13398,7 +15975,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13517,7 +16094,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13572,7 +16149,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C93" s="356">
         <v>0.1</v>
@@ -13593,7 +16170,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -13652,7 +16229,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" s="62"/>
       <c r="D96" s="27"/>
@@ -13673,7 +16250,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
@@ -13730,7 +16307,7 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
@@ -13790,12 +16367,12 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="54"/>
       <c r="D100" s="56"/>
       <c r="E100" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="37"/>
@@ -13813,17 +16390,17 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E101" s="268"/>
       <c r="G101" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="344">
         <f>BS!G32</f>
@@ -13880,7 +16457,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="345">
         <f>BS!C4</f>
@@ -13937,7 +16514,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="345">
         <f>BS!C6+BS!C7</f>
@@ -13994,7 +16571,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" s="344">
         <f>BS!G30</f>
@@ -14051,7 +16628,7 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="344">
         <f>BS!G27</f>
@@ -14112,14 +16689,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
@@ -14135,7 +16712,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -14192,7 +16769,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
@@ -14249,7 +16826,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C111" s="94">
         <f>BS!$G$38/C$4</f>
@@ -14280,14 +16857,14 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -14339,7 +16916,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -14395,7 +16972,7 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
@@ -14449,7 +17026,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
@@ -14503,7 +17080,7 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
@@ -14557,7 +17134,7 @@
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="B120" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C120" s="15">
         <f>C102/C106</f>
@@ -14614,7 +17191,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
@@ -14690,12 +17267,12 @@
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C123" s="54"/>
       <c r="D123" s="56"/>
       <c r="E123" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F123" s="56"/>
       <c r="G123" s="37"/>
@@ -14713,7 +17290,7 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" s="179"/>
       <c r="D124" s="27"/>
@@ -14792,7 +17369,7 @@
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14848,7 +17425,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -15593,7 +18170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15610,32 +18187,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15646,7 +18223,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15656,7 +18233,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15667,7 +18244,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15677,15 +18254,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15695,13 +18272,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15711,13 +18288,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="369"/>
-      <c r="F8" s="369"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15727,13 +18304,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="369"/>
-      <c r="F9" s="369"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15747,7 +18324,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15761,7 +18338,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -15778,7 +18355,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15788,13 +18365,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15804,7 +18381,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15814,7 +18391,7 @@
     </row>
     <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -15831,19 +18408,19 @@
     </row>
     <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="129" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -16609,7 +19186,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16632,7 +19209,7 @@
     <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
@@ -16646,7 +19223,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16867,7 +19444,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -17096,19 +19673,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D73" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17233,20 +19810,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C80" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="3:3">
@@ -17353,7 +19930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -17370,32 +19947,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -17406,7 +19983,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17416,7 +19993,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17427,7 +20004,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17437,13 +20014,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17460,7 +20037,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17470,13 +20047,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17486,7 +20063,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17496,7 +20073,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
@@ -17513,19 +20090,19 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18191,7 +20768,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18214,7 +20791,7 @@
     <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
@@ -18228,7 +20805,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18399,7 +20976,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18618,19 +21195,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D68" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F68" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18755,20 +21332,20 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C75" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="3:3">
@@ -18804,7 +21381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -18819,20 +21396,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18844,14 +21421,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18873,14 +21450,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="107">
         <f>DCF!C3</f>
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18893,7 +21470,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18903,11 +21480,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="371" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洽洽食品(002557.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="371"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18918,7 +21495,7 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
@@ -18928,8 +21505,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="371"/>
-      <c r="F8" s="371"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18940,7 +21517,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
@@ -18950,8 +21527,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="371"/>
-      <c r="F9" s="371"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18961,8 +21538,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="371"/>
-      <c r="F10" s="371"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18973,10 +21550,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>444</v>
-      </c>
-      <c r="E11" s="371"/>
-      <c r="F11" s="371"/>
+        <v>424</v>
+      </c>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18987,15 +21564,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>6.0153753070249838E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="371"/>
-      <c r="F12" s="371"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19006,14 +21583,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9591718766888921E-2</v>
       </c>
-      <c r="E13" s="371"/>
-      <c r="F13" s="371"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19024,18 +21601,18 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.6842771130545571E-2</v>
       </c>
-      <c r="E14" s="371"/>
-      <c r="F14" s="371"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -19044,38 +21621,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="371" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="372"/>
+      <c r="E18" s="377" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="372"/>
-      <c r="F19" s="372"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="372"/>
-      <c r="F20" s="372"/>
+        <v>298</v>
+      </c>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -19085,12 +21662,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -19100,44 +21677,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="372"/>
-      <c r="F22" s="372"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="370"/>
-      <c r="F25" s="370"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="164">
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="370"/>
-      <c r="F26" s="370"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19147,55 +21724,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="370"/>
-      <c r="F27" s="370"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="370"/>
-      <c r="F28" s="370"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="370"/>
-      <c r="F31" s="370"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="164">
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="370"/>
-      <c r="F32" s="370"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19205,55 +21782,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="370"/>
-      <c r="F33" s="370"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="370"/>
-      <c r="F34" s="370"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="370"/>
-      <c r="F37" s="370"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="164">
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="370"/>
-      <c r="F38" s="370"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19263,24 +21840,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="370"/>
-      <c r="F39" s="370"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19293,7 +21870,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19302,12 +21879,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19322,39 +21899,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="370"/>
-      <c r="F49" s="370"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19364,55 +21941,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="370"/>
-      <c r="F51" s="370"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" s="165">
         <v>0.1</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="370"/>
-      <c r="F52" s="370"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="370"/>
-      <c r="F55" s="370"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="164">
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="370"/>
-      <c r="F56" s="370"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19422,23 +21999,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="370"/>
-      <c r="F57" s="370"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C58" s="165">
         <v>0.15</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19449,7 +22026,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19458,7 +22035,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19467,15 +22044,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="252" t="s">
         <v>303</v>
-      </c>
-      <c r="E63" s="252" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19483,24 +22060,24 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C65" s="151">
         <v>5.62138395706255E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
@@ -19511,20 +22088,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19534,19 +22111,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19556,14 +22133,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19572,7 +22149,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19581,12 +22158,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19596,7 +22173,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -19609,12 +22186,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19623,7 +22200,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19635,7 +22212,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19645,7 +22222,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
@@ -19656,7 +22233,7 @@
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19668,12 +22245,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19686,7 +22263,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19698,12 +22275,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19712,7 +22289,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19724,7 +22301,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19734,7 +22311,7 @@
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
@@ -19745,7 +22322,7 @@
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19754,14 +22331,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19772,7 +22349,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19784,7 +22361,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19796,17 +22373,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>21.049942920535798</v>
       </c>
       <c r="D99" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19818,12 +22395,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19832,7 +22409,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19842,7 +22419,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19852,17 +22429,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>20.388648577016472</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19874,32 +22451,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -19918,24 +22495,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6639A61D-07BC-4CF4-8D56-E4716B6AC59B}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D0581F-9BF5-4352-8C4E-B319B6775A8B}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="360"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="358" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
+      <c r="B2" s="379" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D896F325-3174-415A-BD41-339BEE2C9D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37DFE66-4AB2-4A87-AAE5-964CC9513128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4754,8 +4754,22 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4766,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -4790,11 +4795,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>11042.81665836</v>
+        <v>11057.992311119999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.1492528673418922E-2</v>
+        <v>6.098629281479595E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5577,13 +5577,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5595,13 +5595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5621,13 +5621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5678,13 +5678,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5770,7 +5770,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="373"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0662433429876317E-2</v>
+        <v>6.0579182148865506E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.3701328447091167E-2</v>
+        <v>4.3641354071363228E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5951,13 +5951,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6245,13 +6245,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,13 +6413,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
       <c r="B139" s="371" t="s">
@@ -6761,7 +6761,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
       <c r="C179" s="371"/>
@@ -6804,13 +6804,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11042.81665836</v>
+        <v>11057.992311119999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.1492528673418922E-2</v>
+        <v>6.098629281479595E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7299,13 +7299,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7317,13 +7317,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7343,13 +7343,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7378,13 +7378,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7400,13 +7400,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7470,13 +7470,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7492,7 +7492,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="373"/>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0662433429876317E-2</v>
+        <v>6.0579182148865506E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.3701328447091167E-2</v>
+        <v>4.3641354071363228E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7673,13 +7673,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7967,13 +7967,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,13 +8135,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="371" t="s">
@@ -8483,7 +8483,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
       <c r="C179" s="371"/>
@@ -8526,13 +8526,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16174,12 +16174,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.3701328447091167E-2</v>
+        <v>4.3641354071363228E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.3701328447091167E-2</v>
+        <v>4.3641354071363228E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -17373,50 +17373,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0662433429876317E-2</v>
+        <v>6.0579182148865506E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7267796477427288E-2</v>
+        <v>5.7189203893057532E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.2691140036965546E-2</v>
+        <v>5.2618828316878211E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.9203597865834049E-2</v>
+        <v>6.910862495019017E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.409422598298628E-2</v>
+        <v>6.4006265014116673E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.8329991034520044E-2</v>
+        <v>5.8249940726604416E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.0482445139412945E-2</v>
+        <v>4.0426888261362516E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5924273869757201E-2</v>
+        <v>2.5888696183751128E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1505957705112329E-2</v>
+        <v>2.1476443582003756E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.547721461870061E-2</v>
+        <v>2.544225046323121E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.6700884033674564E-2</v>
+        <v>2.6664240551469154E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17430,43 +17430,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6984718509874733E-2</v>
+        <v>7.6879067020611411E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2732425236088388E-2</v>
+        <v>7.2632609464950107E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8604433114378212E-2</v>
+        <v>8.8482835081741831E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4192724987075557E-2</v>
+        <v>8.4077181448666938E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2902313232787105E-2</v>
+        <v>7.2802264312522527E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4648834773792593E-2</v>
+        <v>5.4573836372913645E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9987117930252669E-2</v>
+        <v>3.9932240824218472E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9130886163582715E-2</v>
+        <v>2.9090907820265813E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.251305605333861E-2</v>
+        <v>3.2468436122798802E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3067074216392003E-2</v>
+        <v>3.3021693968153583E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18254,10 +18254,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -18272,8 +18272,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -18288,8 +18288,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -18304,8 +18304,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -20014,8 +20014,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.83</v>
+        <v>-21.86</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21480,11 +21480,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洽洽食品(002557.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -21505,8 +21505,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -21527,8 +21527,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -21538,8 +21538,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -21552,8 +21552,8 @@
       <c r="B11" s="159" t="s">
         <v>424</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -21571,8 +21571,8 @@
         <v>6.0153753070249838E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -21589,8 +21589,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.9591718766888921E-2</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -21607,8 +21607,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.6842771130545571E-2</v>
       </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -21634,21 +21634,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -21656,14 +21656,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -21677,8 +21677,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -21698,8 +21698,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -21709,8 +21709,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -21724,8 +21724,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -21735,8 +21735,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -21756,8 +21756,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -21767,8 +21767,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -21782,8 +21782,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -21793,8 +21793,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -21814,8 +21814,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -21825,8 +21825,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -21840,8 +21840,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -21852,8 +21852,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -21915,8 +21915,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -21926,8 +21926,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -21941,8 +21941,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -21952,8 +21952,8 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -21973,8 +21973,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -21984,8 +21984,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -21999,8 +21999,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -22010,8 +22010,8 @@
         <v>0.15</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -22254,7 +22254,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22267,7 +22267,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.1492528673418922E-2</v>
+        <v>6.098629281479595E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22500,19 +22500,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37DFE66-4AB2-4A87-AAE5-964CC9513128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183050F8-CCA1-4352-A5F4-BF0CF45CA931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,15 +4762,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4780,7 +4771,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>21.86</v>
+        <v>21.83</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>11057.992311119999</v>
+        <v>11042.81665836</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.098629281479595E-2</v>
+        <v>6.1492528673418922E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0579182148865506E-2</v>
+        <v>6.0662433429876317E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.3641354071363228E-2</v>
+        <v>4.3701328447091167E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,15 +6857,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6878,12 +6875,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>21.86</v>
+        <v>21.83</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11057.992311119999</v>
+        <v>11042.81665836</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.098629281479595E-2</v>
+        <v>6.1492528673418922E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0579182148865506E-2</v>
+        <v>6.0662433429876317E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.3641354071363228E-2</v>
+        <v>4.3701328447091167E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,17 +8579,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8606,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16174,12 +16174,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.3641354071363228E-2</v>
+        <v>4.3701328447091167E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.3641354071363228E-2</v>
+        <v>4.3701328447091167E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -17373,50 +17373,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0579182148865506E-2</v>
+        <v>6.0662433429876317E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7189203893057532E-2</v>
+        <v>5.7267796477427288E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.2618828316878211E-2</v>
+        <v>5.2691140036965546E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.910862495019017E-2</v>
+        <v>6.9203597865834049E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.4006265014116673E-2</v>
+        <v>6.409422598298628E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.8249940726604416E-2</v>
+        <v>5.8329991034520044E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.0426888261362516E-2</v>
+        <v>4.0482445139412945E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5888696183751128E-2</v>
+        <v>2.5924273869757201E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1476443582003756E-2</v>
+        <v>2.1505957705112329E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.544225046323121E-2</v>
+        <v>2.547721461870061E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.6664240551469154E-2</v>
+        <v>2.6700884033674564E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17430,43 +17430,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6879067020611411E-2</v>
+        <v>7.6984718509874733E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2632609464950107E-2</v>
+        <v>7.2732425236088388E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8482835081741831E-2</v>
+        <v>8.8604433114378212E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4077181448666938E-2</v>
+        <v>8.4192724987075557E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2802264312522527E-2</v>
+        <v>7.2902313232787105E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4573836372913645E-2</v>
+        <v>5.4648834773792593E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9932240824218472E-2</v>
+        <v>3.9987117930252669E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9090907820265813E-2</v>
+        <v>2.9130886163582715E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2468436122798802E-2</v>
+        <v>3.251305605333861E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3021693968153583E-2</v>
+        <v>3.3067074216392003E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.86</v>
+        <v>-21.83</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21656,7 +21656,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.86</v>
+        <v>21.83</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.86</v>
+        <v>21.83</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22267,7 +22267,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.098629281479595E-2</v>
+        <v>6.1492528673418922E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183050F8-CCA1-4352-A5F4-BF0CF45CA931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE595F14-42CE-41DB-8AC3-1726CFE9858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4762,6 +4762,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4771,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>21.83</v>
+        <v>21.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>11042.81665836</v>
+        <v>10921.411436280001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.1492528673418922E-2</v>
+        <v>6.5577028363230427E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0662433429876317E-2</v>
+        <v>6.1336772662075018E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.3701328447091167E-2</v>
+        <v>4.418712366836499E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>21.83</v>
+        <v>21.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>11042.81665836</v>
+        <v>10921.411436280001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.1492528673418922E-2</v>
+        <v>6.5577028363230427E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0662433429876317E-2</v>
+        <v>6.1336772662075018E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.3701328447091167E-2</v>
+        <v>4.418712366836499E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16174,12 +16174,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.3701328447091167E-2</v>
+        <v>4.418712366836499E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.3701328447091167E-2</v>
+        <v>4.418712366836499E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -17373,50 +17373,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0662433429876317E-2</v>
+        <v>6.1336772662075018E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7267796477427288E-2</v>
+        <v>5.7904400051053156E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.2691140036965546E-2</v>
+        <v>5.3276868318988313E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.9203597865834049E-2</v>
+        <v>6.9972882881480181E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.409422598298628E-2</v>
+        <v>6.4806713904983354E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.8329991034520044E-2</v>
+        <v>5.8978402236385938E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.0482445139412945E-2</v>
+        <v>4.093245842489044E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5924273869757201E-2</v>
+        <v>2.6212454774284376E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1505957705112329E-2</v>
+        <v>2.1745023469319225E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.547721461870061E-2</v>
+        <v>2.5760425897463374E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.6700884033674564E-2</v>
+        <v>2.6997697936781643E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17430,43 +17430,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6984718509874733E-2</v>
+        <v>7.7840500466445806E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2732425236088388E-2</v>
+        <v>7.3540937605549292E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8604433114378212E-2</v>
+        <v>8.9589382810878929E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4192724987075557E-2</v>
+        <v>8.5128632999900825E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2902313232787105E-2</v>
+        <v>7.3712714120969997E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4648834773792593E-2</v>
+        <v>5.5256325294668458E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9987117930252669E-2</v>
+        <v>4.0431625030913187E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9130886163582715E-2</v>
+        <v>2.9454712596156115E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.251305605333861E-2</v>
+        <v>3.2874479557405363E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3067074216392003E-2</v>
+        <v>3.3434656329033682E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.83</v>
+        <v>-21.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21656,7 +21656,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.83</v>
+        <v>21.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.83</v>
+        <v>21.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22267,7 +22267,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.1492528673418922E-2</v>
+        <v>6.5577028363230427E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE595F14-42CE-41DB-8AC3-1726CFE9858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E34526C-8418-4F92-B934-0C8D8C817B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,15 +4762,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4780,7 +4771,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>21.59</v>
+        <v>21.58</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>10921.411436280001</v>
+        <v>10916.352885359998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.5577028363230427E-2</v>
+        <v>6.5748564983868274E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1336772662075018E-2</v>
+        <v>6.1365195633651524E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.418712366836499E-2</v>
+        <v>4.420759962928638E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,15 +6857,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6878,12 +6875,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>21.59</v>
+        <v>21.58</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>10921.411436280001</v>
+        <v>10916.352885359998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.5577028363230427E-2</v>
+        <v>6.5748564983868274E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1336772662075018E-2</v>
+        <v>6.1365195633651524E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.418712366836499E-2</v>
+        <v>4.420759962928638E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,17 +8579,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8606,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16174,12 +16174,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.418712366836499E-2</v>
+        <v>4.420759962928638E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.418712366836499E-2</v>
+        <v>4.420759962928638E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -17373,50 +17373,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.1336772662075018E-2</v>
+        <v>6.1365195633651524E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7904400051053156E-2</v>
+        <v>5.7931232488518891E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3276868318988313E-2</v>
+        <v>5.3301556395132427E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>6.9972882881480181E-2</v>
+        <v>7.00053077576996E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.4806713904983354E-2</v>
+        <v>6.4836744819675191E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.8978402236385938E-2</v>
+        <v>5.9005732357904198E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.093245842489044E-2</v>
+        <v>4.0951426199878807E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6212454774284376E-2</v>
+        <v>2.6224601416904528E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.1745023469319225E-2</v>
+        <v>2.1755099939879615E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.5760425897463374E-2</v>
+        <v>2.5772363073504834E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.6997697936781643E-2</v>
+        <v>2.7010208454824641E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17430,43 +17430,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7840500466445806E-2</v>
+        <v>7.7876571133946498E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3540937605549292E-2</v>
+        <v>7.3575015889889225E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9589382810878929E-2</v>
+        <v>8.9630897816815394E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5128632999900825E-2</v>
+        <v>8.51680809299286E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3712714120969997E-2</v>
+        <v>7.3746872005178057E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5256325294668458E-2</v>
+        <v>5.5281930635398158E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0431625030913187E-2</v>
+        <v>4.0450360723698599E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9454712596156115E-2</v>
+        <v>2.9468361675209023E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2874479557405363E-2</v>
+        <v>3.2889713329211395E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3434656329033682E-2</v>
+        <v>3.3450149682290889E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.59</v>
+        <v>-21.58</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21656,7 +21656,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.59</v>
+        <v>21.58</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.59</v>
+        <v>21.58</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22267,7 +22267,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.5577028363230427E-2</v>
+        <v>6.5748564983868274E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002557.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002557.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E34526C-8418-4F92-B934-0C8D8C817B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CB96E8-C46D-4BF0-8C10-10FEC0D442FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,6 +4762,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4771,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>21.58</v>
+        <v>22.02</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>10916.352885359998</v>
+        <v>11138.929125840001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.5748564983868274E-2</v>
+        <v>5.8302353716981115E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.1365195633651524E-2</v>
+        <v>6.0139006438428691E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.420759962928638E-2</v>
+        <v>4.3324250681198911E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-    